--- a/4.1 Myrmidon Happy reef/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.62668349714151</v>
+        <v>42.29859983747382</v>
       </c>
       <c r="C2" t="n">
-        <v>2.738094347144354</v>
+        <v>2.311034095796991</v>
       </c>
       <c r="D2" t="n">
-        <v>140.8749050731918</v>
+        <v>106.181904700518</v>
       </c>
     </row>
     <row r="3">
@@ -786,13 +786,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>109.8477506281756</v>
+        <v>112.8911685113407</v>
       </c>
       <c r="C3" t="n">
-        <v>12.0951317163207</v>
+        <v>10.38198197241002</v>
       </c>
       <c r="D3" t="n">
-        <v>143.9831183048372</v>
+        <v>113.6225705510046</v>
       </c>
     </row>
     <row r="4">
@@ -800,13 +800,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>147.0520616283127</v>
+        <v>151.6083527237222</v>
       </c>
       <c r="C4" t="n">
-        <v>24.54271085846601</v>
+        <v>20.99467465531804</v>
       </c>
       <c r="D4" t="n">
-        <v>83.53200341583987</v>
+        <v>76.4104055692335</v>
       </c>
     </row>
     <row r="5">
@@ -814,13 +814,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>168.0506632744478</v>
+        <v>170.0632460681537</v>
       </c>
       <c r="C5" t="n">
-        <v>21.86843011209771</v>
+        <v>19.09499284760047</v>
       </c>
       <c r="D5" t="n">
-        <v>44.52225838759286</v>
+        <v>43.46687960552754</v>
       </c>
     </row>
     <row r="6">
@@ -828,13 +828,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>179.8846501014388</v>
+        <v>182.1387428303895</v>
       </c>
       <c r="C6" t="n">
-        <v>12.43776166510284</v>
+        <v>11.63272854762046</v>
       </c>
       <c r="D6" t="n">
-        <v>53.33344403320799</v>
+        <v>50.95859633663495</v>
       </c>
     </row>
     <row r="7">
@@ -842,13 +842,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152.5311955657142</v>
+        <v>157.1424645325614</v>
       </c>
       <c r="C7" t="n">
-        <v>8.024805734513427</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="D7" t="n">
-        <v>60.00638317897354</v>
+        <v>60.48547605864599</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95.9658380901257</v>
+        <v>106.1465617831651</v>
       </c>
       <c r="C8" t="n">
-        <v>7.677267047210056</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="D8" t="n">
-        <v>74.18576527141022</v>
+        <v>74.93680226515903</v>
       </c>
     </row>
     <row r="9">
@@ -870,13 +870,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>36.94218436310322</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="C9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.653124265231384</v>
       </c>
       <c r="D9" t="n">
-        <v>88.19530501101218</v>
+        <v>90.52499231318986</v>
       </c>
     </row>
     <row r="10">
@@ -884,13 +884,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11.24591995214722</v>
+        <v>13.23886779176824</v>
       </c>
       <c r="C10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="D10" t="n">
-        <v>102.2097534891354</v>
+        <v>100.6438659008618</v>
       </c>
     </row>
     <row r="11">
@@ -898,13 +898,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>12.26104707833841</v>
+        <v>11.0171727370577</v>
       </c>
       <c r="D11" t="n">
-        <v>105.7293190088602</v>
+        <v>107.8616750224843</v>
       </c>
     </row>
     <row r="12">
@@ -912,13 +912,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.112582190818895</v>
+        <v>9.329548433457438</v>
       </c>
       <c r="C12" t="n">
-        <v>9.76348091873453</v>
+        <v>12.15010958775853</v>
       </c>
       <c r="D12" t="n">
-        <v>106.5304251355256</v>
+        <v>108.0491888339954</v>
       </c>
     </row>
     <row r="13">
@@ -926,13 +926,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.325220532012953</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>105.6262354999143</v>
+        <v>106.1465617831651</v>
       </c>
     </row>
     <row r="14">
@@ -940,13 +940,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.682175785731292</v>
+        <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>98.02456302593129</v>
+        <v>99.25371115164829</v>
       </c>
     </row>
     <row r="15">
@@ -954,13 +954,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
-        <v>84.92608515587033</v>
+        <v>86.00109889202058</v>
       </c>
     </row>
     <row r="16">
@@ -968,13 +968,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>59.93078860574654</v>
+        <v>62.82399909016188</v>
       </c>
     </row>
     <row r="17">
@@ -982,13 +982,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.249985811684442</v>
+        <v>8.9721922691116</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>33.0554452019901</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -996,13 +996,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.140209995258047</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>10.70104997629023</v>
+        <v>14.98146996680633</v>
       </c>
       <c r="D18" t="n">
-        <v>11.77115497391926</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1010,13 +1010,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>3.009056713516474</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="D19" t="n">
-        <v>1.203622685406589</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>54.61757003036281</v>
+        <v>56.75483478250811</v>
       </c>
       <c r="C2" t="n">
-        <v>2.502474898125119</v>
+        <v>2.091122610045706</v>
       </c>
       <c r="D2" t="n">
-        <v>118.7207863791583</v>
+        <v>89.29388069206439</v>
       </c>
     </row>
     <row r="3">
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>141.3863956271044</v>
+        <v>146.7909167389831</v>
       </c>
       <c r="C3" t="n">
-        <v>11.59444038715483</v>
+        <v>9.92056055141402</v>
       </c>
       <c r="D3" t="n">
-        <v>160.8691788178824</v>
+        <v>125.9484129778233</v>
       </c>
     </row>
     <row r="4">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>209.3851868663512</v>
+        <v>214.0435797230024</v>
       </c>
       <c r="C4" t="n">
-        <v>25.05321966467436</v>
+        <v>21.44136986075034</v>
       </c>
       <c r="D4" t="n">
-        <v>92.15960224076083</v>
+        <v>82.48546036311276</v>
       </c>
     </row>
     <row r="5">
@@ -1125,13 +1125,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>216.9907863311513</v>
+        <v>221.8258937745669</v>
       </c>
       <c r="C5" t="n">
-        <v>25.99177046993431</v>
+        <v>22.35930396422111</v>
       </c>
       <c r="D5" t="n">
-        <v>47.24660826687776</v>
+        <v>45.52854978444584</v>
       </c>
     </row>
     <row r="6">
@@ -1139,13 +1139,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>225.8117894538089</v>
+        <v>228.6696570208714</v>
       </c>
       <c r="C6" t="n">
-        <v>15.73839744678062</v>
+        <v>14.61135108230528</v>
       </c>
       <c r="D6" t="n">
-        <v>53.21268906558563</v>
+        <v>51.40136455125026</v>
       </c>
     </row>
     <row r="7">
@@ -1153,13 +1153,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205.7105052093554</v>
+        <v>209.9025679064893</v>
       </c>
       <c r="C7" t="n">
-        <v>9.402197763571703</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="D7" t="n">
-        <v>59.70695012917827</v>
+        <v>60.18604300885071</v>
       </c>
     </row>
     <row r="8">
@@ -1167,13 +1167,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144.6163455740764</v>
+        <v>157.1336288032232</v>
       </c>
       <c r="C8" t="n">
         <v>8.011061266653972</v>
       </c>
       <c r="D8" t="n">
-        <v>73.68507394224434</v>
+        <v>74.43611093599316</v>
       </c>
     </row>
     <row r="9">
@@ -1181,13 +1181,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70.44530651822986</v>
+        <v>85.75468021825461</v>
       </c>
       <c r="C9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="D9" t="n">
-        <v>88.19530501101218</v>
+        <v>89.52655489797087</v>
       </c>
     </row>
     <row r="10">
@@ -1195,13 +1195,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22.63419332141022</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="C10" t="n">
-        <v>10.2494460323367</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="D10" t="n">
-        <v>100.2168056495144</v>
+        <v>99.93209881528284</v>
       </c>
     </row>
     <row r="11">
@@ -1209,13 +1209,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.950994730245668</v>
+        <v>11.0171727370577</v>
       </c>
       <c r="C11" t="n">
-        <v>12.43874341280708</v>
+        <v>11.19486907152638</v>
       </c>
       <c r="D11" t="n">
-        <v>104.1300519986422</v>
+        <v>105.1962300054542</v>
       </c>
     </row>
     <row r="12">
@@ -1223,13 +1223,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.112582190818895</v>
+        <v>9.329548433457438</v>
       </c>
       <c r="C12" t="n">
-        <v>9.546514676095983</v>
+        <v>12.15010958775853</v>
       </c>
       <c r="D12" t="n">
-        <v>104.3607627091402</v>
+        <v>105.87952640761</v>
       </c>
     </row>
     <row r="13">
@@ -1237,13 +1237,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.585383673638358</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>101.9839515171587</v>
+        <v>103.0246040836603</v>
       </c>
     </row>
     <row r="14">
@@ -1251,13 +1251,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.989462817160544</v>
+        <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>93.72254458592177</v>
+        <v>95.25897974306801</v>
       </c>
     </row>
     <row r="15">
@@ -1268,10 +1268,10 @@
         <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>76.68431317871836</v>
+        <v>78.47600273896879</v>
       </c>
     </row>
     <row r="16">
@@ -1279,13 +1279,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>51.25115715250048</v>
+        <v>54.97099920389165</v>
       </c>
     </row>
     <row r="17">
@@ -1293,13 +1293,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3.305544520199011</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>25.49991487010665</v>
+        <v>29.27768003604838</v>
       </c>
     </row>
     <row r="18">
@@ -1307,13 +1307,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>8.025787482217675</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1321,10 +1321,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.805434028109884</v>
       </c>
       <c r="C19" t="n">
-        <v>1.805434028109884</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="D19" t="n">
         <v>0.6018113427032947</v>
@@ -1394,13 +1394,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>68.29331555052087</v>
+        <v>70.83309686140737</v>
       </c>
       <c r="C2" t="n">
-        <v>1.856484908730718</v>
+        <v>1.544289138780233</v>
       </c>
       <c r="D2" t="n">
-        <v>141.0899078204218</v>
+        <v>105.1510696110589</v>
       </c>
     </row>
     <row r="3">
@@ -1408,13 +1408,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>184.3869450731147</v>
+        <v>192.8152491140736</v>
       </c>
       <c r="C3" t="n">
-        <v>11.02502671869168</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="D3" t="n">
-        <v>168.7918827911541</v>
+        <v>131.5689185846363</v>
       </c>
     </row>
     <row r="4">
@@ -1422,13 +1422,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>272.2415836307533</v>
+        <v>276.3639422408856</v>
       </c>
       <c r="C4" t="n">
-        <v>25.41057582902019</v>
+        <v>21.73491242432013</v>
       </c>
       <c r="D4" t="n">
-        <v>98.74516584084844</v>
+        <v>87.02898873836699</v>
       </c>
     </row>
     <row r="5">
@@ -1436,13 +1436,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>291.186369079604</v>
+        <v>297.0768553050848</v>
       </c>
       <c r="C5" t="n">
-        <v>28.83883881225006</v>
+        <v>24.56823629877644</v>
       </c>
       <c r="D5" t="n">
-        <v>48.62105505282329</v>
+        <v>46.60847225911733</v>
       </c>
     </row>
     <row r="6">
@@ -1450,13 +1450,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>283.935180536037</v>
+        <v>289.650915670162</v>
       </c>
       <c r="C6" t="n">
-        <v>19.28054316370311</v>
+        <v>17.71072858461246</v>
       </c>
       <c r="D6" t="n">
-        <v>53.13218575383738</v>
+        <v>51.36111289537615</v>
       </c>
     </row>
     <row r="7">
@@ -1464,13 +1464,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>260.446866711932</v>
+        <v>264.2796097493116</v>
       </c>
       <c r="C7" t="n">
-        <v>11.07902284242525</v>
+        <v>10.59992996275281</v>
       </c>
       <c r="D7" t="n">
-        <v>59.40751707938298</v>
+        <v>59.88660995905543</v>
       </c>
     </row>
     <row r="8">
@@ -1478,13 +1478,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>196.6882438073272</v>
+        <v>212.4600206760522</v>
       </c>
       <c r="C8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="D8" t="n">
-        <v>73.8519710519663</v>
+        <v>73.93541960682728</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1492,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>111.7140530139488</v>
+        <v>131.2390513560093</v>
       </c>
       <c r="C9" t="n">
-        <v>8.985936736971052</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="D9" t="n">
-        <v>87.19686759579318</v>
+        <v>88.52811748275185</v>
       </c>
     </row>
     <row r="10">
@@ -1506,13 +1506,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42.13661146627311</v>
+        <v>58.64960785170445</v>
       </c>
       <c r="C10" t="n">
-        <v>10.53415286656828</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="D10" t="n">
-        <v>98.22385780989339</v>
+        <v>99.0779783125881</v>
       </c>
     </row>
     <row r="11">
@@ -1520,13 +1520,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.03801042302514</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>12.43874341280708</v>
+        <v>11.55026174046372</v>
       </c>
       <c r="D11" t="n">
-        <v>102.5307849884241</v>
+        <v>103.5969629952362</v>
       </c>
     </row>
     <row r="12">
@@ -1534,13 +1534,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.546514676095983</v>
+        <v>9.980447161373073</v>
       </c>
       <c r="C12" t="n">
-        <v>9.546514676095983</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>101.9741340401162</v>
+        <v>102.6250327680318</v>
       </c>
     </row>
     <row r="13">
@@ -1548,13 +1548,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.585383673638358</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6666888066416</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>98.34166753440302</v>
+        <v>99.64248324253002</v>
       </c>
     </row>
     <row r="14">
@@ -1565,10 +1565,10 @@
         <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>88.80595208305373</v>
+        <v>90.64967427162925</v>
       </c>
     </row>
     <row r="15">
@@ -1576,13 +1576,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>68.80087911361647</v>
+        <v>71.30924449796707</v>
       </c>
     </row>
     <row r="16">
@@ -1590,13 +1590,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.133157834879071</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>43.39815726623026</v>
+        <v>47.11799931762141</v>
       </c>
     </row>
     <row r="17">
@@ -1604,13 +1604,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
-        <v>12.74995743505333</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>19.36104647545135</v>
+        <v>22.66659099565036</v>
       </c>
     </row>
     <row r="18">
@@ -1618,13 +1618,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
+        <v>9.63094497866121</v>
+      </c>
+      <c r="D18" t="n">
         <v>5.885577486959628</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4.815472489330605</v>
       </c>
     </row>
     <row r="19">
@@ -1632,10 +1632,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1705,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.692353115672254</v>
+        <v>3.611849803924016</v>
       </c>
       <c r="C2" t="n">
-        <v>4.173409490753191</v>
+        <v>3.594178345247573</v>
       </c>
       <c r="D2" t="n">
-        <v>16.04764797361836</v>
+        <v>13.18388992033042</v>
       </c>
     </row>
     <row r="3">
@@ -1733,10 +1733,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8040513697781377</v>
+        <v>0.7912886496229291</v>
       </c>
       <c r="C4" t="n">
-        <v>2.34834050855837</v>
+        <v>2.322815068247953</v>
       </c>
       <c r="D4" t="n">
         <v>64.52831310473435</v>
@@ -1761,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.938370878810704</v>
+        <v>2.898119222936585</v>
       </c>
       <c r="C6" t="n">
         <v>3.783655652167208</v>
       </c>
       <c r="D6" t="n">
-        <v>46.16864928761476</v>
+        <v>45.76613272887356</v>
       </c>
     </row>
     <row r="7">
@@ -1778,10 +1778,10 @@
         <v>3.952516257297658</v>
       </c>
       <c r="C7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="D7" t="n">
-        <v>62.40184757733576</v>
+        <v>62.46173418729481</v>
       </c>
     </row>
     <row r="8">
@@ -1795,7 +1795,7 @@
         <v>6.592435834017332</v>
       </c>
       <c r="D8" t="n">
-        <v>78.1912959047372</v>
+        <v>78.27474445959818</v>
       </c>
     </row>
     <row r="9">
@@ -1809,7 +1809,7 @@
         <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>94.85155444580556</v>
+        <v>95.73905437044468</v>
       </c>
     </row>
     <row r="10">
@@ -1823,7 +1823,7 @@
         <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>107.7615367566512</v>
+        <v>106.9074162539564</v>
       </c>
     </row>
     <row r="11">
@@ -1834,10 +1834,10 @@
         <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>9.773298395776996</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>119.411936762948</v>
+        <v>119.5896330974167</v>
       </c>
     </row>
     <row r="12">
@@ -1845,13 +1845,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>9.980447161373073</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>123.2368258186936</v>
+        <v>123.4537920613322</v>
       </c>
     </row>
     <row r="13">
@@ -1862,10 +1862,10 @@
         <v>6.50407854063512</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>126.4392868299467</v>
+        <v>126.6994499715721</v>
       </c>
     </row>
     <row r="14">
@@ -1879,7 +1879,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>125.9876828859932</v>
+        <v>126.2949699174224</v>
       </c>
     </row>
     <row r="15">
@@ -1887,13 +1887,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="C15" t="n">
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>128.6433104259808</v>
+        <v>129.0016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -1907,7 +1907,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>122.3414719124205</v>
+        <v>121.5148403454447</v>
       </c>
     </row>
     <row r="17">
@@ -1915,13 +1915,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.9721922691116</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>104.8329833548829</v>
+        <v>105.3052040006256</v>
       </c>
     </row>
     <row r="18">
@@ -1929,13 +1929,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9.095892479846698</v>
+        <v>9.63094497866121</v>
       </c>
       <c r="C18" t="n">
         <v>20.33199495495144</v>
       </c>
       <c r="D18" t="n">
-        <v>88.81871480320895</v>
+        <v>90.42387229965247</v>
       </c>
     </row>
     <row r="19">
@@ -1949,7 +1949,7 @@
         <v>22.8688310227252</v>
       </c>
       <c r="D19" t="n">
-        <v>67.40287038276901</v>
+        <v>66.80105904006572</v>
       </c>
     </row>
     <row r="20">
@@ -1960,10 +1960,10 @@
         <v>10.08745766113597</v>
       </c>
       <c r="C20" t="n">
-        <v>38.3323391123167</v>
+        <v>28.91737862858979</v>
       </c>
       <c r="D20" t="n">
-        <v>28.91737862858979</v>
+        <v>29.58987580599885</v>
       </c>
     </row>
     <row r="21">
@@ -1971,10 +1971,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>4.254403505467653</v>
+        <v>6.486336353719993</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>12.25196866813776</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2016,13 +2016,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.362305960596078</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C2" t="n">
-        <v>4.675082567623311</v>
+        <v>4.032037821341651</v>
       </c>
       <c r="D2" t="n">
-        <v>58.98536556655686</v>
+        <v>45.93990207252525</v>
       </c>
     </row>
     <row r="3">
@@ -2030,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.83005983617407</v>
+        <v>11.56989669454866</v>
       </c>
       <c r="C3" t="n">
-        <v>4.501313223971626</v>
+        <v>3.946625771072178</v>
       </c>
       <c r="D3" t="n">
-        <v>31.4110177973767</v>
+        <v>30.83669539039231</v>
       </c>
     </row>
     <row r="4">
@@ -2044,10 +2044,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3190680038802134</v>
+        <v>0.3063052837250048</v>
       </c>
       <c r="C4" t="n">
-        <v>2.156899706230242</v>
+        <v>2.144136986075034</v>
       </c>
       <c r="D4" t="n">
         <v>63.94122797759476</v>
@@ -2058,10 +2058,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.497165248976386</v>
+        <v>1.472621556370216</v>
       </c>
       <c r="C5" t="n">
-        <v>3.141592653589794</v>
+        <v>3.092505268377454</v>
       </c>
       <c r="D5" t="n">
         <v>33.72303364087794</v>
@@ -2072,13 +2072,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.978622534684823</v>
+        <v>2.898119222936585</v>
       </c>
       <c r="C6" t="n">
         <v>3.904410619789565</v>
       </c>
       <c r="D6" t="n">
-        <v>47.05418571684538</v>
+        <v>46.249152599363</v>
       </c>
     </row>
     <row r="7">
@@ -2086,13 +2086,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.07228947721577</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="D7" t="n">
-        <v>62.10241452754048</v>
+        <v>62.22218774745859</v>
       </c>
     </row>
     <row r="8">
@@ -2100,13 +2100,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
         <v>6.67588438887831</v>
       </c>
       <c r="D8" t="n">
-        <v>77.69060457557134</v>
+        <v>77.85750168529329</v>
       </c>
     </row>
     <row r="9">
@@ -2120,7 +2120,7 @@
         <v>7.876561831172157</v>
       </c>
       <c r="D9" t="n">
-        <v>93.85311703058655</v>
+        <v>94.74061695522568</v>
       </c>
     </row>
     <row r="10">
@@ -2134,7 +2134,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="D10" t="n">
-        <v>107.3344765053038</v>
+        <v>106.7650628368406</v>
       </c>
     </row>
     <row r="11">
@@ -2142,13 +2142,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.930157044278233</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>10.12869106471434</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="D11" t="n">
-        <v>117.9903660871986</v>
+        <v>118.345758756136</v>
       </c>
     </row>
     <row r="12">
@@ -2156,13 +2156,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.942919764433443</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>9.980447161373073</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>120.199298421754</v>
+        <v>121.7180621202238</v>
       </c>
     </row>
     <row r="13">
@@ -2170,13 +2170,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.50407854063512</v>
+        <v>6.764241682260525</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>124.8783079801943</v>
+        <v>124.0978185553181</v>
       </c>
     </row>
     <row r="14">
@@ -2190,7 +2190,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>123.5293866345592</v>
+        <v>123.8366736659884</v>
       </c>
     </row>
     <row r="15">
@@ -2198,13 +2198,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.600109889202059</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>125.0599313054799</v>
+        <v>125.41826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2212,13 +2212,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>115.3151035931261</v>
+        <v>114.0751562426624</v>
       </c>
     </row>
     <row r="17">
@@ -2226,13 +2226,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.499971623368884</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>97.74967366874218</v>
+        <v>98.69411496022761</v>
       </c>
     </row>
     <row r="18">
@@ -2240,13 +2240,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.560839981032187</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
         <v>20.86704745376595</v>
       </c>
       <c r="D18" t="n">
-        <v>79.18776982454773</v>
+        <v>81.32797981980576</v>
       </c>
     </row>
     <row r="19">
@@ -2257,7 +2257,7 @@
         <v>9.027170140549421</v>
       </c>
       <c r="C19" t="n">
-        <v>27.68332176435156</v>
+        <v>24.07245370813179</v>
       </c>
       <c r="D19" t="n">
         <v>51.15396412978005</v>
@@ -2268,13 +2268,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>12.10494919336317</v>
       </c>
       <c r="C20" t="n">
-        <v>22.19240685449914</v>
+        <v>29.58987580599885</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -2327,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.883613991551134</v>
+        <v>5.995533229835271</v>
       </c>
       <c r="C2" t="n">
-        <v>4.084070449666731</v>
+        <v>3.519565519724815</v>
       </c>
       <c r="D2" t="n">
-        <v>65.11736172728244</v>
+        <v>50.42550733322891</v>
       </c>
     </row>
     <row r="3">
@@ -2341,13 +2341,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.27170743436489</v>
+        <v>19.18825887950391</v>
       </c>
       <c r="C3" t="n">
-        <v>7.814711725804611</v>
+        <v>6.78387663634546</v>
       </c>
       <c r="D3" t="n">
-        <v>40.44309667644735</v>
+        <v>37.30641276137879</v>
       </c>
     </row>
     <row r="4">
@@ -2355,13 +2355,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.76494569252429</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="C4" t="n">
-        <v>4.211697651218816</v>
+        <v>3.879866927183394</v>
       </c>
       <c r="D4" t="n">
-        <v>63.45624461169684</v>
+        <v>63.37966829076559</v>
       </c>
     </row>
     <row r="5">
@@ -2369,10 +2369,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8099418560036188</v>
+        <v>0.7608544707912782</v>
       </c>
       <c r="C5" t="n">
-        <v>3.264311116620645</v>
+        <v>3.215223731408305</v>
       </c>
       <c r="D5" t="n">
         <v>35.2447425824605</v>
@@ -2383,13 +2383,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.535854320069512</v>
+        <v>2.455351008321273</v>
       </c>
       <c r="C6" t="n">
-        <v>4.145920555034281</v>
+        <v>4.065417243286043</v>
       </c>
       <c r="D6" t="n">
-        <v>47.97997380195012</v>
+        <v>46.77242412572655</v>
       </c>
     </row>
     <row r="7">
@@ -2397,13 +2397,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.19206269713388</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="D7" t="n">
-        <v>61.8029814777452</v>
+        <v>61.98264130762237</v>
       </c>
     </row>
     <row r="8">
@@ -2411,13 +2411,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>6.759332943739289</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="D8" t="n">
-        <v>77.18991324640547</v>
+        <v>77.4402589109884</v>
       </c>
     </row>
     <row r="9">
@@ -2425,13 +2425,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
         <v>7.987499321752047</v>
       </c>
       <c r="D9" t="n">
-        <v>92.96561710594743</v>
+        <v>93.85311703058655</v>
       </c>
     </row>
     <row r="10">
@@ -2445,7 +2445,7 @@
         <v>9.110618695410402</v>
       </c>
       <c r="D10" t="n">
-        <v>106.9074162539564</v>
+        <v>106.4803560026091</v>
       </c>
     </row>
     <row r="11">
@@ -2453,13 +2453,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.285549713215578</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>10.48408373365169</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="D11" t="n">
-        <v>116.3910990769806</v>
+        <v>116.9241880803866</v>
       </c>
     </row>
     <row r="12">
@@ -2467,13 +2467,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>9.980447161373073</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>117.5957035100914</v>
+        <v>119.9823321791154</v>
       </c>
     </row>
     <row r="13">
@@ -2481,13 +2481,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.764241682260525</v>
+        <v>7.024404823885929</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>123.0571659888165</v>
+        <v>121.496187139064</v>
       </c>
     </row>
     <row r="14">
@@ -2501,7 +2501,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>120.7638033516959</v>
+        <v>121.3783774145544</v>
       </c>
     </row>
     <row r="15">
@@ -2509,7 +2509,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.958447801252145</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
         <v>13.61684065790326</v>
@@ -2523,13 +2523,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.439684102782329</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>108.2887352738317</v>
+        <v>107.048787923368</v>
       </c>
     </row>
     <row r="17">
@@ -2537,13 +2537,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.02775097762617</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>89.72192269111601</v>
+        <v>91.61080527408687</v>
       </c>
     </row>
     <row r="18">
@@ -2551,13 +2551,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.025787482217675</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>22.47220495020949</v>
+        <v>21.40209995258047</v>
       </c>
       <c r="D18" t="n">
-        <v>67.41661485062848</v>
+        <v>69.55682484588651</v>
       </c>
     </row>
     <row r="19">
@@ -2565,13 +2565,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>9.027170140549421</v>
       </c>
       <c r="C19" t="n">
         <v>25.27607639353838</v>
       </c>
       <c r="D19" t="n">
-        <v>36.10868056219768</v>
+        <v>37.31230324760427</v>
       </c>
     </row>
     <row r="20">
@@ -2579,13 +2579,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>4.03498306445439</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>12.77744637077223</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>8.06996612890878</v>
+        <v>9.41496048372691</v>
       </c>
     </row>
     <row r="21">
@@ -2638,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.693375921105506</v>
+        <v>8.742463306317847</v>
       </c>
       <c r="C2" t="n">
-        <v>5.467352964950488</v>
+        <v>4.707480241863456</v>
       </c>
       <c r="D2" t="n">
-        <v>105.7577896922834</v>
+        <v>81.27496544377645</v>
       </c>
     </row>
     <row r="3">
@@ -2652,13 +2652,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.50656611985813</v>
+        <v>22.85508655486575</v>
       </c>
       <c r="C3" t="n">
-        <v>9.694758579437254</v>
+        <v>8.389034132788995</v>
       </c>
       <c r="D3" t="n">
-        <v>49.90714454538661</v>
+        <v>44.10501561328795</v>
       </c>
     </row>
     <row r="4">
@@ -2666,13 +2666,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.31368590593603</v>
+        <v>37.72660077879643</v>
       </c>
       <c r="C4" t="n">
-        <v>7.67039481328033</v>
+        <v>6.828055283036567</v>
       </c>
       <c r="D4" t="n">
-        <v>64.13266877992288</v>
+        <v>63.67321085433538</v>
       </c>
     </row>
     <row r="5">
@@ -2680,10 +2680,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.40272184738622</v>
+        <v>25.47635292520474</v>
       </c>
       <c r="C5" t="n">
-        <v>4.147884050442775</v>
+        <v>3.951534509593412</v>
       </c>
       <c r="D5" t="n">
         <v>36.66827675361837</v>
@@ -2694,13 +2694,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.690569546713008</v>
+        <v>1.56981457909065</v>
       </c>
       <c r="C6" t="n">
-        <v>4.387430490278996</v>
+        <v>4.306927178530758</v>
       </c>
       <c r="D6" t="n">
-        <v>48.90576188705487</v>
+        <v>47.33594730796422</v>
       </c>
     </row>
     <row r="7">
@@ -2708,13 +2708,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.832743037379548</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="D7" t="n">
-        <v>61.50354842794993</v>
+        <v>61.74309486778615</v>
       </c>
     </row>
     <row r="8">
@@ -2722,13 +2722,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>6.842781498600267</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="D8" t="n">
-        <v>76.68922191723958</v>
+        <v>77.02301613668349</v>
       </c>
     </row>
     <row r="9">
@@ -2736,13 +2736,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>8.209374302911826</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="D9" t="n">
-        <v>92.07811718130831</v>
+        <v>92.96561710594743</v>
       </c>
     </row>
     <row r="10">
@@ -2756,7 +2756,7 @@
         <v>9.252972112526189</v>
       </c>
       <c r="D10" t="n">
-        <v>106.3380025854933</v>
+        <v>106.1956491683775</v>
       </c>
     </row>
     <row r="11">
@@ -2767,10 +2767,10 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>10.83947640258903</v>
+        <v>10.12869106471434</v>
       </c>
       <c r="D11" t="n">
-        <v>113.7256540599505</v>
+        <v>115.5026174046372</v>
       </c>
     </row>
     <row r="12">
@@ -2778,13 +2778,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
-        <v>9.76348091873453</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>116.2939060542602</v>
+        <v>117.1617710248143</v>
       </c>
     </row>
     <row r="13">
@@ -2792,13 +2792,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.024404823885929</v>
+        <v>7.544731107136739</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>121.2360239974386</v>
+        <v>120.195371430937</v>
       </c>
     </row>
     <row r="14">
@@ -2812,7 +2812,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>117.9982200688326</v>
+        <v>118.6127941316911</v>
       </c>
     </row>
     <row r="15">
@@ -2820,10 +2820,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.958447801252145</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>115.7431455921777</v>
@@ -2834,13 +2834,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>101.2623669545373</v>
+        <v>100.0224196040735</v>
       </c>
     </row>
     <row r="17">
@@ -2848,13 +2848,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>80.7497304220044</v>
+        <v>83.5830542964607</v>
       </c>
     </row>
     <row r="18">
@@ -2862,13 +2862,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>23.007257449024</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="D18" t="n">
-        <v>55.1104073778947</v>
+        <v>57.25061737315275</v>
       </c>
     </row>
     <row r="19">
@@ -2876,13 +2876,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>20.46158565191202</v>
+        <v>23.47064236542849</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>26.47969907894496</v>
       </c>
     </row>
     <row r="20">
@@ -2890,13 +2890,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.017491532227195</v>
+        <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>7.397468951499714</v>
+        <v>12.77744637077223</v>
       </c>
       <c r="D20" t="n">
-        <v>4.03498306445439</v>
+        <v>4.707480241863455</v>
       </c>
     </row>
     <row r="21">
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.92823460659875</v>
+        <v>12.0951317163207</v>
       </c>
       <c r="C2" t="n">
-        <v>4.460079820393259</v>
+        <v>3.838633523605029</v>
       </c>
       <c r="D2" t="n">
-        <v>104.7613157724729</v>
+        <v>80.26572880381072</v>
       </c>
     </row>
     <row r="3">
@@ -2963,13 +2963,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.84298678724529</v>
+        <v>32.06388002070083</v>
       </c>
       <c r="C3" t="n">
-        <v>12.41419972020092</v>
+        <v>10.71577619185394</v>
       </c>
       <c r="D3" t="n">
-        <v>66.66557785687966</v>
+        <v>56.47503668679776</v>
       </c>
     </row>
     <row r="4">
@@ -2977,13 +2977,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.87296330218722</v>
+        <v>48.02611594404971</v>
       </c>
       <c r="C4" t="n">
-        <v>11.37158365829081</v>
+        <v>9.993209881528283</v>
       </c>
       <c r="D4" t="n">
-        <v>65.94497504196249</v>
+        <v>64.79633022799374</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.94703634836225</v>
+        <v>53.18618187757097</v>
       </c>
       <c r="C5" t="n">
-        <v>6.185010536754907</v>
+        <v>5.718680377237671</v>
       </c>
       <c r="D5" t="n">
-        <v>38.04272353956391</v>
+        <v>38.01817984695774</v>
       </c>
     </row>
     <row r="6">
@@ -3005,13 +3005,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.72709950041517</v>
+        <v>27.85414586489051</v>
       </c>
       <c r="C6" t="n">
-        <v>4.830198704894308</v>
+        <v>4.669192081397831</v>
       </c>
       <c r="D6" t="n">
-        <v>49.87180162803373</v>
+        <v>47.93972214607601</v>
       </c>
     </row>
     <row r="7">
@@ -3019,13 +3019,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.934443887993716</v>
+        <v>2.694897448157494</v>
       </c>
       <c r="C7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="D7" t="n">
-        <v>61.20411537815465</v>
+        <v>61.50354842794993</v>
       </c>
     </row>
     <row r="8">
@@ -3033,13 +3033,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>7.009678608322226</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="D8" t="n">
-        <v>76.18853058807372</v>
+        <v>76.60577336237861</v>
       </c>
     </row>
     <row r="9">
@@ -3047,13 +3047,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>8.320311793491715</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="D9" t="n">
-        <v>91.30155474724909</v>
+        <v>92.1890546718882</v>
       </c>
     </row>
     <row r="10">
@@ -3061,13 +3061,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
         <v>9.395325529641976</v>
       </c>
       <c r="D10" t="n">
-        <v>105.6262354999143</v>
+        <v>105.7685889170301</v>
       </c>
     </row>
     <row r="11">
@@ -3078,10 +3078,10 @@
         <v>7.996335051090269</v>
       </c>
       <c r="C11" t="n">
-        <v>11.19486907152638</v>
+        <v>10.30638739918301</v>
       </c>
       <c r="D11" t="n">
-        <v>112.1263870497324</v>
+        <v>114.0810467288878</v>
       </c>
     </row>
     <row r="12">
@@ -3089,13 +3089,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.810784734987623</v>
+        <v>8.027750977626168</v>
       </c>
       <c r="C12" t="n">
-        <v>9.76348091873453</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>113.6903111425976</v>
+        <v>115.426041083706</v>
       </c>
     </row>
     <row r="13">
@@ -3103,13 +3103,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.284567965511334</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>119.1547188644354</v>
+        <v>117.593740014683</v>
       </c>
     </row>
     <row r="14">
@@ -3117,13 +3117,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.067601722872788</v>
+        <v>7.37488875430204</v>
       </c>
       <c r="C14" t="n">
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>114.6180627231109</v>
+        <v>115.5399238173986</v>
       </c>
     </row>
     <row r="15">
@@ -3131,10 +3131,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.958447801252145</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>110.3680769114264</v>
@@ -3145,13 +3145,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.613052535806514</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>93.82268285175492</v>
+        <v>92.99605128477911</v>
       </c>
     </row>
     <row r="17">
@@ -3159,13 +3159,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>70.83309686140737</v>
+        <v>74.13864138160638</v>
       </c>
     </row>
     <row r="18">
@@ -3173,13 +3173,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="C18" t="n">
         <v>21.93715245139498</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>46.014514898048</v>
       </c>
     </row>
     <row r="19">
@@ -3187,13 +3187,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>15.64709491028566</v>
+        <v>19.85977430920873</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>18.05434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -3201,10 +3201,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>4.03498306445439</v>
+        <v>8.06996612890878</v>
       </c>
       <c r="D20" t="n">
         <v>2.017491532227195</v>
@@ -3260,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.15974713835175</v>
+        <v>14.65552972899638</v>
       </c>
       <c r="C2" t="n">
-        <v>3.994731408580272</v>
+        <v>3.429244730934109</v>
       </c>
       <c r="D2" t="n">
-        <v>119.4688781297944</v>
+        <v>91.1523290962036</v>
       </c>
     </row>
     <row r="3">
@@ -3274,13 +3274,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>43.65832040785565</v>
+        <v>44.71369918992098</v>
       </c>
       <c r="C3" t="n">
-        <v>13.45485228670254</v>
+        <v>11.6042578641973</v>
       </c>
       <c r="D3" t="n">
-        <v>82.38826734039233</v>
+        <v>68.09892950508001</v>
       </c>
     </row>
     <row r="4">
@@ -3288,13 +3288,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>66.02155136289375</v>
+        <v>65.62590703808229</v>
       </c>
       <c r="C4" t="n">
-        <v>15.74919667152733</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="D4" t="n">
-        <v>68.06358658772712</v>
+        <v>65.97050048227291</v>
       </c>
     </row>
     <row r="5">
@@ -3302,13 +3302,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.18929135159972</v>
+        <v>73.26292242941824</v>
       </c>
       <c r="C5" t="n">
-        <v>9.27751580513236</v>
+        <v>8.320311793491719</v>
       </c>
       <c r="D5" t="n">
-        <v>39.44171401811561</v>
+        <v>39.34353924769093</v>
       </c>
     </row>
     <row r="6">
@@ -3316,13 +3316,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.96617258082844</v>
+        <v>65.97246397768143</v>
       </c>
       <c r="C6" t="n">
-        <v>5.715735134124931</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="D6" t="n">
-        <v>50.87809302488671</v>
+        <v>48.5434969841878</v>
       </c>
     </row>
     <row r="7">
@@ -3330,13 +3330,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.95464398362217</v>
+        <v>26.17044855210722</v>
       </c>
       <c r="C7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="D7" t="n">
-        <v>60.90468232835937</v>
+        <v>61.26400198811371</v>
       </c>
     </row>
     <row r="8">
@@ -3344,13 +3344,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>7.176575718044183</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="D8" t="n">
-        <v>75.68783925890784</v>
+        <v>76.18853058807372</v>
       </c>
     </row>
     <row r="9">
@@ -3358,13 +3358,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>8.431249284071605</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="D9" t="n">
-        <v>90.52499231318986</v>
+        <v>91.41249223782897</v>
       </c>
     </row>
     <row r="10">
@@ -3372,13 +3372,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
         <v>9.537678946757763</v>
       </c>
       <c r="D10" t="n">
-        <v>104.9144684143354</v>
+        <v>105.3415286656828</v>
       </c>
     </row>
     <row r="11">
@@ -3389,10 +3389,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>11.55026174046372</v>
+        <v>10.48408373365169</v>
       </c>
       <c r="D11" t="n">
-        <v>110.5271200395144</v>
+        <v>112.6594760531384</v>
       </c>
     </row>
     <row r="12">
@@ -3400,13 +3400,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.244717220264713</v>
+        <v>8.461683462903258</v>
       </c>
       <c r="C12" t="n">
-        <v>9.76348091873453</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>112.1715474441278</v>
+        <v>113.6903111425976</v>
       </c>
     </row>
     <row r="13">
@@ -3414,13 +3414,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.544731107136739</v>
+        <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>115.7725980233051</v>
+        <v>114.9921085984289</v>
       </c>
     </row>
     <row r="14">
@@ -3428,13 +3428,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.067601722872788</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>110.9306183459598</v>
+        <v>111.8524794402476</v>
       </c>
     </row>
     <row r="15">
@@ -3442,10 +3442,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.958447801252145</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>104.634670318625</v>
@@ -3456,10 +3456,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>85.55636718199678</v>
@@ -3470,13 +3470,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>60.91646330081034</v>
+        <v>64.69422846675207</v>
       </c>
     </row>
     <row r="18">
@@ -3484,13 +3484,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>19.79694245613693</v>
+        <v>20.86704745376595</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>35.84851742057228</v>
       </c>
     </row>
     <row r="19">
@@ -3498,13 +3498,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.407245370813179</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
+        <v>16.24890625298896</v>
+      </c>
+      <c r="D19" t="n">
         <v>11.4344155113626</v>
-      </c>
-      <c r="D19" t="n">
-        <v>10.23079282595601</v>
       </c>
     </row>
     <row r="20">
@@ -3512,10 +3512,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="C20" t="n">
-        <v>2.017491532227195</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="D20" t="n">
         <v>0.672497177409065</v>
@@ -3571,13 +3571,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.50478255089888</v>
+        <v>21.36184829670635</v>
       </c>
       <c r="C2" t="n">
-        <v>3.274128593663113</v>
+        <v>2.797980957103409</v>
       </c>
       <c r="D2" t="n">
-        <v>150.4538174235279</v>
+        <v>114.2067104350315</v>
       </c>
     </row>
     <row r="3">
@@ -3585,13 +3585,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>52.72966919509619</v>
+        <v>54.48699758569798</v>
       </c>
       <c r="C3" t="n">
-        <v>13.74937659797658</v>
+        <v>11.83987731321653</v>
       </c>
       <c r="D3" t="n">
-        <v>99.81919782929445</v>
+        <v>80.98927686184062</v>
       </c>
     </row>
     <row r="4">
@@ -3599,13 +3599,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>90.20690605701392</v>
+        <v>91.3555508709827</v>
       </c>
       <c r="C4" t="n">
-        <v>19.47591095684822</v>
+        <v>16.77021428394402</v>
       </c>
       <c r="D4" t="n">
-        <v>71.59886007071988</v>
+        <v>68.22950194974482</v>
       </c>
     </row>
     <row r="5">
@@ -3613,13 +3613,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>100.8745766113598</v>
+        <v>99.47558613280809</v>
       </c>
       <c r="C5" t="n">
-        <v>13.10633185169492</v>
+        <v>11.78097245096173</v>
       </c>
       <c r="D5" t="n">
-        <v>40.86524818927349</v>
+        <v>40.64435495581795</v>
       </c>
     </row>
     <row r="6">
@@ -3627,13 +3627,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>96.60397409788615</v>
+        <v>97.93227874173209</v>
       </c>
       <c r="C6" t="n">
-        <v>7.366053024963819</v>
+        <v>6.923284810348508</v>
       </c>
       <c r="D6" t="n">
-        <v>51.88438442173969</v>
+        <v>49.1875234781737</v>
       </c>
     </row>
     <row r="7">
@@ -3641,13 +3641,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>64.43799231594365</v>
+        <v>68.33062196328224</v>
       </c>
       <c r="C7" t="n">
-        <v>6.28809404570082</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="D7" t="n">
-        <v>60.6052492785641</v>
+        <v>61.02445554827749</v>
       </c>
     </row>
     <row r="8">
@@ -3655,13 +3655,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.02627050830318</v>
+        <v>22.19731559302038</v>
       </c>
       <c r="C8" t="n">
-        <v>7.34347282776614</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="D8" t="n">
-        <v>75.18714792974197</v>
+        <v>75.77128781376882</v>
       </c>
     </row>
     <row r="9">
@@ -3669,13 +3669,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>8.542186774651494</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="D9" t="n">
-        <v>89.74842987913063</v>
+        <v>91.52342972840887</v>
       </c>
     </row>
     <row r="10">
@@ -3683,13 +3683,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
         <v>9.680032363873552</v>
       </c>
       <c r="D10" t="n">
-        <v>104.0603479116407</v>
+        <v>103.7756410774091</v>
       </c>
     </row>
     <row r="11">
@@ -3700,10 +3700,10 @@
         <v>8.529424054496287</v>
       </c>
       <c r="C11" t="n">
-        <v>11.72795807493239</v>
+        <v>10.66178006812036</v>
       </c>
       <c r="D11" t="n">
-        <v>108.9278530292963</v>
+        <v>111.0602090429204</v>
       </c>
     </row>
     <row r="12">
@@ -3711,13 +3711,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.678649705541803</v>
+        <v>8.895615948180348</v>
       </c>
       <c r="C12" t="n">
-        <v>9.76348091873453</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>110.4358175030194</v>
+        <v>111.9545812014893</v>
       </c>
     </row>
     <row r="13">
@@ -3725,13 +3725,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.804894248762142</v>
+        <v>8.585383673638358</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>112.3904771821749</v>
+        <v>112.1303140405495</v>
       </c>
     </row>
     <row r="14">
@@ -3739,13 +3739,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.067601722872788</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>106.9358869373796</v>
+        <v>107.8577480316673</v>
       </c>
     </row>
     <row r="15">
@@ -3753,10 +3753,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.958447801252145</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>98.54292581377359</v>
@@ -3767,13 +3767,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>77.29005151223865</v>
+        <v>78.11668307921445</v>
       </c>
     </row>
     <row r="17">
@@ -3781,13 +3781,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>50.99982974021331</v>
+        <v>54.77759490615504</v>
       </c>
     </row>
     <row r="18">
@@ -3795,13 +3795,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.280419990516093</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>24.07736244665303</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="19">
@@ -3809,13 +3809,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>7.823547455142832</v>
+        <v>12.63803819676919</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>6.619924769736241</v>
       </c>
     </row>
     <row r="20">
@@ -3823,10 +3823,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>0.672497177409065</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -3882,13 +3882,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.86262174133023</v>
+        <v>32.59304203328985</v>
       </c>
       <c r="C2" t="n">
-        <v>2.507383636646354</v>
+        <v>2.13628300444106</v>
       </c>
       <c r="D2" t="n">
-        <v>157.3820109723977</v>
+        <v>118.9514970896563</v>
       </c>
     </row>
     <row r="3">
@@ -3896,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>73.19420009012094</v>
+        <v>77.00828992111981</v>
       </c>
       <c r="C3" t="n">
-        <v>13.17505419099219</v>
+        <v>11.32445976848696</v>
       </c>
       <c r="D3" t="n">
-        <v>122.0803270230909</v>
+        <v>97.47772955466581</v>
       </c>
     </row>
     <row r="4">
@@ -3910,13 +3910,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>110.2571394208465</v>
+        <v>111.878004880558</v>
       </c>
       <c r="C4" t="n">
-        <v>22.69211643596077</v>
+        <v>19.37380919560656</v>
       </c>
       <c r="D4" t="n">
-        <v>76.62737181187205</v>
+        <v>71.61162279087509</v>
       </c>
     </row>
     <row r="5">
@@ -3924,13 +3924,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>135.5302705712722</v>
+        <v>136.5856493533375</v>
       </c>
       <c r="C5" t="n">
-        <v>17.25421590213769</v>
+        <v>15.46252634188727</v>
       </c>
       <c r="D5" t="n">
-        <v>42.38695713085605</v>
+        <v>41.99425804915732</v>
       </c>
     </row>
     <row r="6">
@@ -3938,13 +3938,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>134.4002789636841</v>
+        <v>134.4405306195582</v>
       </c>
       <c r="C6" t="n">
-        <v>9.620145753914496</v>
+        <v>9.016370915802709</v>
       </c>
       <c r="D6" t="n">
-        <v>52.93092747446678</v>
+        <v>49.87180162803373</v>
       </c>
     </row>
     <row r="7">
@@ -3952,13 +3952,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106.2987326773234</v>
+        <v>111.329207913884</v>
       </c>
       <c r="C7" t="n">
-        <v>7.006733365209485</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="D7" t="n">
-        <v>60.30581622876881</v>
+        <v>60.78490910844126</v>
       </c>
     </row>
     <row r="8">
@@ -3966,13 +3966,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53.24017800130452</v>
+        <v>60.4167537193487</v>
       </c>
       <c r="C8" t="n">
-        <v>7.510369937488099</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="D8" t="n">
-        <v>74.68645660057609</v>
+        <v>75.35404503946393</v>
       </c>
     </row>
     <row r="9">
@@ -3980,13 +3980,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.42187377538564</v>
+        <v>17.30624853046277</v>
       </c>
       <c r="C9" t="n">
-        <v>8.653124265231384</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="D9" t="n">
-        <v>88.97186744507141</v>
+        <v>91.52342972840887</v>
       </c>
     </row>
     <row r="10">
@@ -3994,13 +3994,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
         <v>9.82238578098934</v>
       </c>
       <c r="D10" t="n">
-        <v>103.2062274089459</v>
+        <v>102.2097534891354</v>
       </c>
     </row>
     <row r="11">
@@ -4008,13 +4008,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.529424054496287</v>
       </c>
       <c r="C11" t="n">
-        <v>12.08335074386974</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="D11" t="n">
-        <v>107.3285860190783</v>
+        <v>109.4609420327023</v>
       </c>
     </row>
     <row r="12">
@@ -4022,13 +4022,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.895615948180348</v>
+        <v>9.112582190818895</v>
       </c>
       <c r="C12" t="n">
-        <v>9.76348091873453</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>108.4831213192725</v>
+        <v>110.0018850177424</v>
       </c>
     </row>
     <row r="13">
@@ -4036,13 +4036,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.065057390387548</v>
+        <v>8.845546815263763</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>109.0083563410446</v>
+        <v>109.26851948267</v>
       </c>
     </row>
     <row r="14">
@@ -4050,13 +4050,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.37488875430204</v>
+        <v>7.989462817160544</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>102.6338684973701</v>
+        <v>103.5557295916578</v>
       </c>
     </row>
     <row r="15">
@@ -4064,13 +4064,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.600109889202059</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
-        <v>91.73450548482195</v>
+        <v>92.45118130892213</v>
       </c>
     </row>
     <row r="16">
@@ -4078,13 +4078,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>68.61042005899259</v>
+        <v>70.67699897643212</v>
       </c>
     </row>
     <row r="17">
@@ -4092,13 +4092,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>41.55541682535899</v>
+        <v>45.33318199130072</v>
       </c>
     </row>
     <row r="18">
@@ -4106,13 +4106,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>17.12167996206437</v>
+        <v>19.79694245613693</v>
       </c>
     </row>
     <row r="19">
@@ -4120,13 +4120,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>4.814490741626358</v>
+        <v>9.628981483252716</v>
       </c>
       <c r="D19" t="n">
-        <v>3.009056713516474</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -4134,10 +4134,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.34499435481813</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>

--- a/4.1 Myrmidon Happy reef/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.29859983747382</v>
+        <v>41.5053476924424</v>
       </c>
       <c r="C2" t="n">
-        <v>2.311034095796991</v>
+        <v>3.700207097306228</v>
       </c>
       <c r="D2" t="n">
-        <v>106.181904700518</v>
+        <v>155.7032223981356</v>
       </c>
     </row>
     <row r="3">
@@ -786,13 +786,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>112.8911685113407</v>
+        <v>110.7607759931252</v>
       </c>
       <c r="C3" t="n">
-        <v>10.38198197241002</v>
+        <v>13.83773389135879</v>
       </c>
       <c r="D3" t="n">
-        <v>113.6225705510046</v>
+        <v>154.5810847721815</v>
       </c>
     </row>
     <row r="4">
@@ -800,13 +800,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>151.6083527237222</v>
+        <v>146.9627225872263</v>
       </c>
       <c r="C4" t="n">
-        <v>20.99467465531804</v>
+        <v>24.24916829489622</v>
       </c>
       <c r="D4" t="n">
-        <v>76.4104055692335</v>
+        <v>89.82402445235768</v>
       </c>
     </row>
     <row r="5">
@@ -814,13 +814,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>170.0632460681537</v>
+        <v>169.0324109786946</v>
       </c>
       <c r="C5" t="n">
-        <v>19.09499284760047</v>
+        <v>21.15666302651877</v>
       </c>
       <c r="D5" t="n">
-        <v>43.46687960552754</v>
+        <v>55.34602682691395</v>
       </c>
     </row>
     <row r="6">
@@ -828,13 +828,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182.1387428303895</v>
+        <v>179.3211269192012</v>
       </c>
       <c r="C6" t="n">
-        <v>11.63272854762046</v>
+        <v>13.00128484734051</v>
       </c>
       <c r="D6" t="n">
-        <v>50.95859633663495</v>
+        <v>48.98626519880311</v>
       </c>
     </row>
     <row r="7">
@@ -842,13 +842,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157.1424645325614</v>
+        <v>155.3458662337898</v>
       </c>
       <c r="C7" t="n">
-        <v>7.665486074759095</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="D7" t="n">
-        <v>60.48547605864599</v>
+        <v>55.75443387188061</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106.1465617831651</v>
+        <v>111.4038207394068</v>
       </c>
       <c r="C8" t="n">
-        <v>7.593818492349078</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="D8" t="n">
-        <v>74.93680226515903</v>
+        <v>68.59471209572465</v>
       </c>
     </row>
     <row r="9">
@@ -870,13 +870,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46.48280855297372</v>
+        <v>57.90937008270233</v>
       </c>
       <c r="C9" t="n">
-        <v>8.653124265231384</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>90.52499231318986</v>
+        <v>83.6468678972367</v>
       </c>
     </row>
     <row r="10">
@@ -884,13 +884,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13.23886779176824</v>
+        <v>16.79770321966293</v>
       </c>
       <c r="C10" t="n">
-        <v>9.964739198105127</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>100.6438659008618</v>
+        <v>94.80737579911448</v>
       </c>
     </row>
     <row r="11">
@@ -898,13 +898,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>11.0171727370577</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="D11" t="n">
-        <v>107.8616750224843</v>
+        <v>106.4401043467349</v>
       </c>
     </row>
     <row r="12">
@@ -912,13 +912,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.329548433457438</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>12.15010958775853</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>108.0491888339954</v>
+        <v>111.0867162309351</v>
       </c>
     </row>
     <row r="13">
@@ -926,13 +926,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="D13" t="n">
-        <v>106.1465617831651</v>
+        <v>115.5124348816797</v>
       </c>
     </row>
     <row r="14">
@@ -943,10 +943,10 @@
         <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>99.25371115164829</v>
+        <v>115.8472108488279</v>
       </c>
     </row>
     <row r="15">
@@ -954,13 +954,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>86.00109889202058</v>
+        <v>116.818159328328</v>
       </c>
     </row>
     <row r="16">
@@ -971,10 +971,10 @@
         <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>11.5728419376614</v>
       </c>
       <c r="D16" t="n">
-        <v>62.82399909016188</v>
+        <v>115.728419376614</v>
       </c>
     </row>
     <row r="17">
@@ -982,13 +982,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.9721922691116</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>103.4163214176548</v>
       </c>
     </row>
     <row r="18">
@@ -996,13 +996,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
         <v>14.98146996680633</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>88.28366230439441</v>
       </c>
     </row>
     <row r="19">
@@ -1010,13 +1010,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3.009056713516474</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>6.619924769736241</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>1.805434028109884</v>
+        <v>73.42098380980195</v>
       </c>
     </row>
     <row r="20">
@@ -1024,13 +1024,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>0.672497177409065</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>51.78228266049801</v>
       </c>
     </row>
     <row r="21">
@@ -1038,13 +1038,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>48.59483127677039</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>77.11788441748344</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>20.07177813605733</v>
       </c>
     </row>
   </sheetData>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>56.75483478250811</v>
+        <v>53.53666580798706</v>
       </c>
       <c r="C2" t="n">
-        <v>2.091122610045706</v>
+        <v>3.566689409528662</v>
       </c>
       <c r="D2" t="n">
-        <v>89.29388069206439</v>
+        <v>131.7417061805837</v>
       </c>
     </row>
     <row r="3">
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>146.7909167389831</v>
+        <v>137.3563213011712</v>
       </c>
       <c r="C3" t="n">
-        <v>9.92056055141402</v>
+        <v>13.55302705712722</v>
       </c>
       <c r="D3" t="n">
-        <v>125.9484129778233</v>
+        <v>173.6024465419635</v>
       </c>
     </row>
     <row r="4">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>214.0435797230024</v>
+        <v>198.5496374545792</v>
       </c>
       <c r="C4" t="n">
-        <v>21.44136986075034</v>
+        <v>25.29571134762332</v>
       </c>
       <c r="D4" t="n">
-        <v>82.48546036311276</v>
+        <v>98.20913159432968</v>
       </c>
     </row>
     <row r="5">
@@ -1125,13 +1125,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>221.8258937745669</v>
+        <v>207.6641831408066</v>
       </c>
       <c r="C5" t="n">
-        <v>22.35930396422111</v>
+        <v>24.69095476180729</v>
       </c>
       <c r="D5" t="n">
-        <v>45.52854978444584</v>
+        <v>57.62859023928778</v>
       </c>
     </row>
     <row r="6">
@@ -1139,13 +1139,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>228.6696570208714</v>
+        <v>218.1237231818521</v>
       </c>
       <c r="C6" t="n">
-        <v>14.61135108230528</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>51.40136455125026</v>
+        <v>49.54978838104078</v>
       </c>
     </row>
     <row r="7">
@@ -1153,13 +1153,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>209.9025679064893</v>
+        <v>204.6924328400515</v>
       </c>
       <c r="C7" t="n">
-        <v>8.982991493858314</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="D7" t="n">
-        <v>60.18604300885071</v>
+        <v>55.27534099220816</v>
       </c>
     </row>
     <row r="8">
@@ -1167,13 +1167,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157.1336288032232</v>
+        <v>159.2198426747477</v>
       </c>
       <c r="C8" t="n">
-        <v>8.011061266653972</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="D8" t="n">
-        <v>74.43611093599316</v>
+        <v>67.5098808825319</v>
       </c>
     </row>
     <row r="9">
@@ -1181,13 +1181,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.75468021825461</v>
+        <v>100.6203039559598</v>
       </c>
       <c r="C9" t="n">
-        <v>8.764061755811273</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>89.52655489797087</v>
+        <v>82.20468051969816</v>
       </c>
     </row>
     <row r="10">
@@ -1195,13 +1195,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31.17539834835747</v>
+        <v>44.69897297435728</v>
       </c>
       <c r="C10" t="n">
-        <v>10.10709261522091</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>99.93209881528284</v>
+        <v>93.3838416279566</v>
       </c>
     </row>
     <row r="11">
@@ -1209,13 +1209,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.0171727370577</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="C11" t="n">
-        <v>11.19486907152638</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>105.1962300054542</v>
+        <v>104.6631410020482</v>
       </c>
     </row>
     <row r="12">
@@ -1223,13 +1223,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.329548433457438</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>12.15010958775853</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>105.87952640761</v>
+        <v>109.5679525324653</v>
       </c>
     </row>
     <row r="13">
@@ -1237,13 +1237,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.365873098514571</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="D13" t="n">
-        <v>103.0246040836603</v>
+        <v>113.6912928903019</v>
       </c>
     </row>
     <row r="14">
@@ -1254,10 +1254,10 @@
         <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>95.25897974306801</v>
+        <v>114.3107756916816</v>
       </c>
     </row>
     <row r="15">
@@ -1265,13 +1265,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>78.47600273896879</v>
+        <v>116.1014835042278</v>
       </c>
     </row>
     <row r="16">
@@ -1282,10 +1282,10 @@
         <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>11.15952615417349</v>
       </c>
       <c r="D16" t="n">
-        <v>54.97099920389165</v>
+        <v>113.6618404591745</v>
       </c>
     </row>
     <row r="17">
@@ -1293,13 +1293,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.499971623368884</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>12.74995743505333</v>
       </c>
       <c r="D17" t="n">
-        <v>29.27768003604838</v>
+        <v>101.9996594804266</v>
       </c>
     </row>
     <row r="18">
@@ -1307,13 +1307,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>12.30620747273377</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>9.095892479846698</v>
+        <v>87.2135573067654</v>
       </c>
     </row>
     <row r="19">
@@ -1321,13 +1321,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.805434028109884</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>4.212679398923063</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6018113427032947</v>
+        <v>72.21736112439537</v>
       </c>
     </row>
     <row r="20">
@@ -1335,13 +1335,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>18.15742379004475</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>51.10978548308893</v>
       </c>
     </row>
     <row r="21">
@@ -1349,13 +1349,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>48.94715057699965</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>81.5785842949994</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>21.75428914533317</v>
       </c>
     </row>
   </sheetData>
@@ -1394,13 +1394,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>70.83309686140737</v>
+        <v>64.23673403657305</v>
       </c>
       <c r="C2" t="n">
-        <v>1.544289138780233</v>
+        <v>2.747911824186823</v>
       </c>
       <c r="D2" t="n">
-        <v>105.1510696110589</v>
+        <v>159.1805727665778</v>
       </c>
     </row>
     <row r="3">
@@ -1408,13 +1408,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>192.8152491140736</v>
+        <v>171.4131491614931</v>
       </c>
       <c r="C3" t="n">
-        <v>9.395325529641976</v>
+        <v>13.22414157620454</v>
       </c>
       <c r="D3" t="n">
-        <v>131.5689185846363</v>
+        <v>181.0686378327605</v>
       </c>
     </row>
     <row r="4">
@@ -1422,13 +1422,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>276.3639422408856</v>
+        <v>246.5119397978528</v>
       </c>
       <c r="C4" t="n">
-        <v>21.73491242432013</v>
+        <v>25.89555919491812</v>
       </c>
       <c r="D4" t="n">
-        <v>87.02898873836699</v>
+        <v>107.8322225913569</v>
       </c>
     </row>
     <row r="5">
@@ -1436,13 +1436,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>297.0768553050848</v>
+        <v>267.1826377107695</v>
       </c>
       <c r="C5" t="n">
-        <v>24.56823629877644</v>
+        <v>27.83254741539708</v>
       </c>
       <c r="D5" t="n">
-        <v>46.60847225911733</v>
+        <v>60.35294011857268</v>
       </c>
     </row>
     <row r="6">
@@ -1450,13 +1450,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>289.650915670162</v>
+        <v>264.6546373723339</v>
       </c>
       <c r="C6" t="n">
-        <v>17.71072858461246</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="D6" t="n">
-        <v>51.36111289537615</v>
+        <v>50.2340665309008</v>
       </c>
     </row>
     <row r="7">
@@ -1464,13 +1464,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264.2796097493116</v>
+        <v>247.8107920105714</v>
       </c>
       <c r="C7" t="n">
-        <v>10.59992996275281</v>
+        <v>11.97732199181109</v>
       </c>
       <c r="D7" t="n">
-        <v>59.88660995905543</v>
+        <v>54.85613472249477</v>
       </c>
     </row>
     <row r="8">
@@ -1478,13 +1478,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>212.4600206760522</v>
+        <v>210.2903582496668</v>
       </c>
       <c r="C8" t="n">
-        <v>8.511752595819845</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="D8" t="n">
-        <v>73.93541960682728</v>
+        <v>66.50849822420017</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1492,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131.2390513560093</v>
+        <v>147.2140499995134</v>
       </c>
       <c r="C9" t="n">
-        <v>8.874999246391162</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="D9" t="n">
-        <v>88.52811748275185</v>
+        <v>80.76249314215958</v>
       </c>
     </row>
     <row r="10">
@@ -1506,13 +1506,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58.64960785170445</v>
+        <v>81.42615459023047</v>
       </c>
       <c r="C10" t="n">
-        <v>10.2494460323367</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>99.0779783125881</v>
+        <v>91.96030745679873</v>
       </c>
     </row>
     <row r="11">
@@ -1520,13 +1520,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>19.54659679155399</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="C11" t="n">
-        <v>11.55026174046372</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>103.5969629952362</v>
+        <v>102.8861776573615</v>
       </c>
     </row>
     <row r="12">
@@ -1534,13 +1534,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.980447161373073</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="C12" t="n">
-        <v>11.93314334511998</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>102.6250327680318</v>
+        <v>109.1340200471882</v>
       </c>
     </row>
     <row r="13">
@@ -1548,13 +1548,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.365873098514571</v>
+        <v>7.284567965511334</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="D13" t="n">
-        <v>99.64248324253002</v>
+        <v>111.8701508989241</v>
       </c>
     </row>
     <row r="14">
@@ -1562,13 +1562,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8.296749848589794</v>
+        <v>7.989462817160544</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>90.64967427162925</v>
+        <v>112.4670535031061</v>
       </c>
     </row>
     <row r="15">
@@ -1576,13 +1576,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>71.30924449796707</v>
+        <v>113.9514560319273</v>
       </c>
     </row>
     <row r="16">
@@ -1593,10 +1593,10 @@
         <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>10.74621037068559</v>
       </c>
       <c r="D16" t="n">
-        <v>47.11799931762141</v>
+        <v>111.5952615417349</v>
       </c>
     </row>
     <row r="17">
@@ -1607,10 +1607,10 @@
         <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>12.27773678931061</v>
       </c>
       <c r="D17" t="n">
-        <v>22.66659099565036</v>
+        <v>100.5829975431985</v>
       </c>
     </row>
     <row r="18">
@@ -1618,13 +1618,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.745367491701582</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>9.63094497866121</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>5.885577486959628</v>
+        <v>86.14345230913638</v>
       </c>
     </row>
     <row r="19">
@@ -1632,13 +1632,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>2.407245370813179</v>
+        <v>15.64709491028566</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>71.01373843898878</v>
       </c>
     </row>
     <row r="20">
@@ -1646,13 +1646,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>17.48492661263569</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>50.43728830567987</v>
       </c>
     </row>
     <row r="21">
@@ -1660,13 +1660,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>49.14494411637857</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>84.88672165556298</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>23.45554151008977</v>
       </c>
     </row>
   </sheetData>
@@ -1705,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.611849803924016</v>
+        <v>3.710024574348697</v>
       </c>
       <c r="C2" t="n">
-        <v>3.594178345247573</v>
+        <v>4.299073196896783</v>
       </c>
       <c r="D2" t="n">
-        <v>13.18388992033042</v>
+        <v>16.10458934046468</v>
       </c>
     </row>
     <row r="3">
@@ -1719,13 +1719,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.08344855486097889</v>
+        <v>0.07853981633974483</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6724971774090651</v>
+        <v>0.6675884388878311</v>
       </c>
       <c r="D3" t="n">
-        <v>30.92505268377453</v>
+        <v>30.49308369390593</v>
       </c>
     </row>
     <row r="4">
@@ -1733,13 +1733,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7912886496229291</v>
+        <v>0.7657632093125121</v>
       </c>
       <c r="C4" t="n">
-        <v>2.322815068247953</v>
+        <v>2.271764187627119</v>
       </c>
       <c r="D4" t="n">
-        <v>64.52831310473435</v>
+        <v>64.26029598147497</v>
       </c>
     </row>
     <row r="5">
@@ -1747,13 +1747,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.88986433067511</v>
+        <v>1.84077694546277</v>
       </c>
       <c r="C5" t="n">
-        <v>2.847068342315751</v>
+        <v>2.896155727528091</v>
       </c>
       <c r="D5" t="n">
-        <v>32.05406254365837</v>
+        <v>34.53297549688156</v>
       </c>
     </row>
     <row r="6">
@@ -1761,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.898119222936585</v>
+        <v>2.857867567062466</v>
       </c>
       <c r="C6" t="n">
-        <v>3.783655652167208</v>
+        <v>3.703152340418969</v>
       </c>
       <c r="D6" t="n">
-        <v>45.76613272887356</v>
+        <v>45.00135126726531</v>
       </c>
     </row>
     <row r="7">
@@ -1775,13 +1775,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.952516257297658</v>
+        <v>3.832743037379548</v>
       </c>
       <c r="C7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="D7" t="n">
-        <v>62.46173418729481</v>
+        <v>61.6832082578271</v>
       </c>
     </row>
     <row r="8">
@@ -1789,13 +1789,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>6.592435834017332</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>78.27474445959818</v>
+        <v>77.4402589109884</v>
       </c>
     </row>
     <row r="9">
@@ -1803,13 +1803,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>95.73905437044468</v>
+        <v>94.2968669929061</v>
       </c>
     </row>
     <row r="10">
@@ -1820,10 +1820,10 @@
         <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>106.9074162539564</v>
+        <v>106.6227094197249</v>
       </c>
     </row>
     <row r="11">
@@ -1837,7 +1837,7 @@
         <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>119.5896330974167</v>
+        <v>119.0565440940107</v>
       </c>
     </row>
     <row r="12">
@@ -1848,7 +1848,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
         <v>123.4537920613322</v>
@@ -1862,10 +1862,10 @@
         <v>6.50407854063512</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>126.6994499715721</v>
+        <v>127.7401025380738</v>
       </c>
     </row>
     <row r="14">
@@ -1873,13 +1873,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.067601722872788</v>
+        <v>6.760314691443536</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>126.2949699174224</v>
+        <v>127.2168310117102</v>
       </c>
     </row>
     <row r="15">
@@ -1887,13 +1887,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.883434065101886</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>129.0016483380309</v>
+        <v>129.359986250081</v>
       </c>
     </row>
     <row r="16">
@@ -1904,10 +1904,10 @@
         <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>121.5148403454447</v>
+        <v>129.3678402317149</v>
       </c>
     </row>
     <row r="17">
@@ -1915,13 +1915,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>105.3052040006256</v>
+        <v>110.0274104580528</v>
       </c>
     </row>
     <row r="18">
@@ -1929,13 +1929,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9.63094497866121</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>20.33199495495144</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>90.42387229965247</v>
+        <v>96.84450228542661</v>
       </c>
     </row>
     <row r="19">
@@ -1946,10 +1946,10 @@
         <v>9.628981483252716</v>
       </c>
       <c r="C19" t="n">
-        <v>22.8688310227252</v>
+        <v>21.66520833731861</v>
       </c>
       <c r="D19" t="n">
-        <v>66.80105904006572</v>
+        <v>78.23547455142831</v>
       </c>
     </row>
     <row r="20">
@@ -1960,10 +1960,10 @@
         <v>10.08745766113597</v>
       </c>
       <c r="C20" t="n">
-        <v>28.91737862858979</v>
+        <v>24.20989838672634</v>
       </c>
       <c r="D20" t="n">
-        <v>29.58987580599885</v>
+        <v>53.12727701531613</v>
       </c>
     </row>
     <row r="21">
@@ -1971,13 +1971,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6.486336353719993</v>
+        <v>17.12765163770884</v>
       </c>
       <c r="C21" t="n">
-        <v>12.25196866813776</v>
+        <v>33.47677365552183</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.33558885968757</v>
       </c>
     </row>
   </sheetData>
@@ -2016,13 +2016,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.350524988145117</v>
+        <v>5.813909904549611</v>
       </c>
       <c r="C2" t="n">
-        <v>4.032037821341651</v>
+        <v>4.895975801078843</v>
       </c>
       <c r="D2" t="n">
-        <v>45.93990207252525</v>
+        <v>60.24102088028854</v>
       </c>
     </row>
     <row r="3">
@@ -2030,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.56989669454866</v>
+        <v>11.73679380427062</v>
       </c>
       <c r="C3" t="n">
-        <v>3.946625771072178</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="D3" t="n">
-        <v>30.83669539039231</v>
+        <v>31.38156536624929</v>
       </c>
     </row>
     <row r="4">
@@ -2044,13 +2044,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3063052837250048</v>
+        <v>0.2807798434145877</v>
       </c>
       <c r="C4" t="n">
-        <v>2.144136986075034</v>
+        <v>2.067560665143783</v>
       </c>
       <c r="D4" t="n">
-        <v>63.94122797759476</v>
+        <v>62.55009148067703</v>
       </c>
     </row>
     <row r="5">
@@ -2058,13 +2058,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.472621556370216</v>
+        <v>1.349903093339365</v>
       </c>
       <c r="C5" t="n">
         <v>3.092505268377454</v>
       </c>
       <c r="D5" t="n">
-        <v>33.72303364087794</v>
+        <v>38.26361677301944</v>
       </c>
     </row>
     <row r="6">
@@ -2072,13 +2072,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.898119222936585</v>
+        <v>2.777364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>3.904410619789565</v>
+        <v>3.823907308041327</v>
       </c>
       <c r="D6" t="n">
-        <v>46.249152599363</v>
+        <v>45.12210623488766</v>
       </c>
     </row>
     <row r="7">
@@ -2086,13 +2086,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.012402867256713</v>
+        <v>3.832743037379548</v>
       </c>
       <c r="C7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="D7" t="n">
-        <v>62.22218774745859</v>
+        <v>60.66513588852315</v>
       </c>
     </row>
     <row r="8">
@@ -2100,13 +2100,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>6.67588438887831</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>77.85750168529329</v>
+        <v>76.2719791429347</v>
       </c>
     </row>
     <row r="9">
@@ -2114,13 +2114,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>7.876561831172157</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>94.74061695522568</v>
+        <v>92.74374212478766</v>
       </c>
     </row>
     <row r="10">
@@ -2128,13 +2128,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>106.7650628368406</v>
+        <v>105.0568218314512</v>
       </c>
     </row>
     <row r="11">
@@ -2145,10 +2145,10 @@
         <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>9.773298395776996</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>118.345758756136</v>
+        <v>117.2795807493239</v>
       </c>
     </row>
     <row r="12">
@@ -2159,10 +2159,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>121.7180621202238</v>
+        <v>121.9350283628623</v>
       </c>
     </row>
     <row r="13">
@@ -2170,13 +2170,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.764241682260525</v>
+        <v>7.024404823885929</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>124.0978185553181</v>
+        <v>126.1791236883213</v>
       </c>
     </row>
     <row r="14">
@@ -2184,13 +2184,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.067601722872788</v>
+        <v>6.760314691443536</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>123.8366736659884</v>
+        <v>125.6803958545639</v>
       </c>
     </row>
     <row r="15">
@@ -2198,13 +2198,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>125.41826921753</v>
+        <v>127.5682966898305</v>
       </c>
     </row>
     <row r="16">
@@ -2212,13 +2212,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>114.0751562426624</v>
+        <v>128.954524448227</v>
       </c>
     </row>
     <row r="17">
@@ -2226,13 +2226,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>98.69411496022761</v>
+        <v>109.0829691665674</v>
       </c>
     </row>
     <row r="18">
@@ -2240,13 +2240,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9.095892479846698</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>20.86704745376595</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>81.32797981980576</v>
+        <v>95.7743972877976</v>
       </c>
     </row>
     <row r="19">
@@ -2257,10 +2257,10 @@
         <v>9.027170140549421</v>
       </c>
       <c r="C19" t="n">
-        <v>24.07245370813179</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="D19" t="n">
-        <v>51.15396412978005</v>
+        <v>77.63366320872503</v>
       </c>
     </row>
     <row r="20">
@@ -2268,13 +2268,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12.10494919336317</v>
+        <v>9.41496048372691</v>
       </c>
       <c r="C20" t="n">
-        <v>29.58987580599885</v>
+        <v>23.53740120931727</v>
       </c>
       <c r="D20" t="n">
-        <v>16.81242943522663</v>
+        <v>53.12727701531613</v>
       </c>
     </row>
     <row r="21">
@@ -2282,13 +2282,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22.74706248330653</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>38.99496425709691</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4.874370532137114</v>
       </c>
     </row>
   </sheetData>
@@ -2327,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.995533229835271</v>
+        <v>6.937029278207961</v>
       </c>
       <c r="C2" t="n">
-        <v>3.519565519724815</v>
+        <v>4.329507375728434</v>
       </c>
       <c r="D2" t="n">
-        <v>50.42550733322891</v>
+        <v>66.58212930201867</v>
       </c>
     </row>
     <row r="3">
@@ -2341,13 +2341,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.18825887950391</v>
+        <v>20.33690369347268</v>
       </c>
       <c r="C3" t="n">
-        <v>6.78387663634546</v>
+        <v>8.060148651866312</v>
       </c>
       <c r="D3" t="n">
-        <v>37.30641276137879</v>
+        <v>42.77474747403353</v>
       </c>
     </row>
     <row r="4">
@@ -2355,13 +2355,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.30548776693678</v>
+        <v>20.3310132072472</v>
       </c>
       <c r="C4" t="n">
-        <v>3.879866927183394</v>
+        <v>4.288273972150068</v>
       </c>
       <c r="D4" t="n">
-        <v>63.37966829076559</v>
+        <v>61.13342954344888</v>
       </c>
     </row>
     <row r="5">
@@ -2369,13 +2369,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7608544707912782</v>
+        <v>0.6381360077604269</v>
       </c>
       <c r="C5" t="n">
-        <v>3.215223731408305</v>
+        <v>3.141592653589794</v>
       </c>
       <c r="D5" t="n">
-        <v>35.2447425824605</v>
+        <v>41.45429681182157</v>
       </c>
     </row>
     <row r="6">
@@ -2383,13 +2383,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.455351008321273</v>
+        <v>2.173589417202439</v>
       </c>
       <c r="C6" t="n">
-        <v>4.065417243286043</v>
+        <v>3.984913931537804</v>
       </c>
       <c r="D6" t="n">
-        <v>46.77242412572655</v>
+        <v>45.60512610537709</v>
       </c>
     </row>
     <row r="7">
@@ -2397,13 +2397,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.07228947721577</v>
+        <v>3.772856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="D7" t="n">
-        <v>61.98264130762237</v>
+        <v>59.76683673913732</v>
       </c>
     </row>
     <row r="8">
@@ -2411,13 +2411,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>6.67588438887831</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="D8" t="n">
-        <v>77.4402589109884</v>
+        <v>75.10369937488099</v>
       </c>
     </row>
     <row r="9">
@@ -2425,13 +2425,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>7.987499321752047</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>93.85311703058655</v>
+        <v>91.30155474724909</v>
       </c>
     </row>
     <row r="10">
@@ -2439,13 +2439,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>9.110618695410402</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>106.4803560026091</v>
+        <v>103.6332876602933</v>
       </c>
     </row>
     <row r="11">
@@ -2453,13 +2453,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>9.950994730245668</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>116.9241880803866</v>
+        <v>115.5026174046372</v>
       </c>
     </row>
     <row r="12">
@@ -2467,13 +2467,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>119.9823321791154</v>
+        <v>120.4162646643925</v>
       </c>
     </row>
     <row r="13">
@@ -2481,13 +2481,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.024404823885929</v>
+        <v>7.544731107136739</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D13" t="n">
-        <v>121.496187139064</v>
+        <v>124.6181448385689</v>
       </c>
     </row>
     <row r="14">
@@ -2498,10 +2498,10 @@
         <v>7.067601722872788</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>121.3783774145544</v>
+        <v>124.1439606974177</v>
       </c>
     </row>
     <row r="15">
@@ -2509,13 +2509,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>120.7598763608789</v>
+        <v>126.8516208657304</v>
       </c>
     </row>
     <row r="16">
@@ -2523,13 +2523,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>7.439684102782329</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>107.048787923368</v>
+        <v>126.8879455307875</v>
       </c>
     </row>
     <row r="17">
@@ -2537,13 +2537,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>8.02775097762617</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>91.61080527408687</v>
+        <v>108.1385278750819</v>
       </c>
     </row>
     <row r="18">
@@ -2554,10 +2554,10 @@
         <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>21.40209995258047</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>69.55682484588651</v>
+        <v>94.70429229016857</v>
       </c>
     </row>
     <row r="19">
@@ -2565,13 +2565,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9.027170140549421</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>25.27607639353838</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="D19" t="n">
-        <v>37.31230324760427</v>
+        <v>77.03185186602173</v>
       </c>
     </row>
     <row r="20">
@@ -2582,10 +2582,10 @@
         <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D20" t="n">
-        <v>9.41496048372691</v>
+        <v>53.12727701531613</v>
       </c>
     </row>
     <row r="21">
@@ -2593,13 +2593,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>27.95088486088985</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>44.89081507961097</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6.775972087488448</v>
       </c>
     </row>
   </sheetData>
@@ -2638,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.742463306317847</v>
+        <v>10.48506548135594</v>
       </c>
       <c r="C2" t="n">
-        <v>4.707480241863456</v>
+        <v>6.029894399483909</v>
       </c>
       <c r="D2" t="n">
-        <v>81.27496544377645</v>
+        <v>110.27873787034</v>
       </c>
     </row>
     <row r="3">
@@ -2652,13 +2652,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.85508655486575</v>
+        <v>25.34872572365265</v>
       </c>
       <c r="C3" t="n">
-        <v>8.389034132788995</v>
+        <v>9.940195505498956</v>
       </c>
       <c r="D3" t="n">
-        <v>44.10501561328795</v>
+        <v>54.57535487908019</v>
       </c>
     </row>
     <row r="4">
@@ -2666,13 +2666,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.72660077879643</v>
+        <v>38.83695743229957</v>
       </c>
       <c r="C4" t="n">
-        <v>6.828055283036567</v>
+        <v>7.785259294677207</v>
       </c>
       <c r="D4" t="n">
-        <v>63.67321085433538</v>
+        <v>61.56736202872597</v>
       </c>
     </row>
     <row r="5">
@@ -2680,13 +2680,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.47635292520474</v>
+        <v>25.45180923259857</v>
       </c>
       <c r="C5" t="n">
-        <v>3.951534509593412</v>
+        <v>4.123340357836605</v>
       </c>
       <c r="D5" t="n">
-        <v>36.66827675361837</v>
+        <v>44.57134577280519</v>
       </c>
     </row>
     <row r="6">
@@ -2694,13 +2694,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.56981457909065</v>
+        <v>1.207549676223577</v>
       </c>
       <c r="C6" t="n">
-        <v>4.306927178530758</v>
+        <v>4.145920555034281</v>
       </c>
       <c r="D6" t="n">
-        <v>47.33594730796422</v>
+        <v>45.68562941712533</v>
       </c>
     </row>
     <row r="7">
@@ -2708,13 +2708,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.653083207502381</v>
+        <v>3.114103717870883</v>
       </c>
       <c r="C7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="D7" t="n">
-        <v>61.74309486778615</v>
+        <v>58.92842419971054</v>
       </c>
     </row>
     <row r="8">
@@ -2722,13 +2722,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>6.759332943739289</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="D8" t="n">
-        <v>77.02301613668349</v>
+        <v>73.93541960682728</v>
       </c>
     </row>
     <row r="9">
@@ -2736,13 +2736,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>8.098436812331936</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>92.96561710594743</v>
+        <v>89.85936736971051</v>
       </c>
     </row>
     <row r="10">
@@ -2750,13 +2750,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>9.252972112526189</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>106.1956491683775</v>
+        <v>102.2097534891354</v>
       </c>
     </row>
     <row r="11">
@@ -2764,13 +2764,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>10.12869106471434</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>115.5026174046372</v>
+        <v>113.7256540599505</v>
       </c>
     </row>
     <row r="12">
@@ -2781,10 +2781,10 @@
         <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>117.1617710248143</v>
+        <v>118.8975009659227</v>
       </c>
     </row>
     <row r="13">
@@ -2792,13 +2792,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.544731107136739</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D13" t="n">
-        <v>120.195371430937</v>
+        <v>123.0571659888165</v>
       </c>
     </row>
     <row r="14">
@@ -2806,13 +2806,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.067601722872788</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>118.6127941316911</v>
+        <v>122.6075255402714</v>
       </c>
     </row>
     <row r="15">
@@ -2820,13 +2820,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>115.7431455921777</v>
+        <v>126.1349450416302</v>
       </c>
     </row>
     <row r="16">
@@ -2834,13 +2834,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>100.0224196040735</v>
+        <v>124.821366613348</v>
       </c>
     </row>
     <row r="17">
@@ -2848,13 +2848,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>83.5830542964607</v>
+        <v>107.1940865835965</v>
       </c>
     </row>
     <row r="18">
@@ -2862,13 +2862,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.560839981032187</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="C18" t="n">
-        <v>21.93715245139498</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>57.25061737315275</v>
+        <v>93.63418729253954</v>
       </c>
     </row>
     <row r="19">
@@ -2879,10 +2879,10 @@
         <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>23.47064236542849</v>
+        <v>19.85977430920873</v>
       </c>
       <c r="D19" t="n">
-        <v>26.47969907894496</v>
+        <v>76.43004052331844</v>
       </c>
     </row>
     <row r="20">
@@ -2890,13 +2890,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.052474596681584</v>
+        <v>8.06996612890878</v>
       </c>
       <c r="C20" t="n">
-        <v>12.77744637077223</v>
+        <v>22.19240685449914</v>
       </c>
       <c r="D20" t="n">
-        <v>4.707480241863455</v>
+        <v>53.12727701531613</v>
       </c>
     </row>
     <row r="21">
@@ -2904,13 +2904,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>32.6480931893993</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>50.29571112961514</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>8.823808970107921</v>
       </c>
     </row>
   </sheetData>
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.0951317163207</v>
+        <v>14.20883452356409</v>
       </c>
       <c r="C2" t="n">
-        <v>3.838633523605029</v>
+        <v>5.037347470490384</v>
       </c>
       <c r="D2" t="n">
-        <v>80.26572880381072</v>
+        <v>109.4511245556599</v>
       </c>
     </row>
     <row r="3">
@@ -2963,13 +2963,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32.06388002070083</v>
+        <v>37.27205159173015</v>
       </c>
       <c r="C3" t="n">
-        <v>10.71577619185394</v>
+        <v>12.89525609528186</v>
       </c>
       <c r="D3" t="n">
-        <v>56.47503668679776</v>
+        <v>75.71238295151402</v>
       </c>
     </row>
     <row r="4">
@@ -2977,13 +2977,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.02611594404971</v>
+        <v>50.37445645260809</v>
       </c>
       <c r="C4" t="n">
-        <v>9.993209881528283</v>
+        <v>11.52473630015331</v>
       </c>
       <c r="D4" t="n">
-        <v>64.79633022799374</v>
+        <v>64.3113468620958</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.18618187757097</v>
+        <v>53.82431788533139</v>
       </c>
       <c r="C5" t="n">
-        <v>5.718680377237671</v>
+        <v>6.234097921967248</v>
       </c>
       <c r="D5" t="n">
-        <v>38.01817984695774</v>
+        <v>46.31394794784328</v>
       </c>
     </row>
     <row r="6">
@@ -3005,13 +3005,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.85414586489051</v>
+        <v>28.82018560586937</v>
       </c>
       <c r="C6" t="n">
-        <v>4.669192081397831</v>
+        <v>4.588688769649592</v>
       </c>
       <c r="D6" t="n">
-        <v>47.93972214607601</v>
+        <v>46.00764266411829</v>
       </c>
     </row>
     <row r="7">
@@ -3019,13 +3019,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.694897448157494</v>
+        <v>1.976258128648829</v>
       </c>
       <c r="C7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="D7" t="n">
-        <v>61.50354842794993</v>
+        <v>58.14989827024283</v>
       </c>
     </row>
     <row r="8">
@@ -3033,13 +3033,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>6.842781498600267</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>76.60577336237861</v>
+        <v>72.85058839363457</v>
       </c>
     </row>
     <row r="9">
@@ -3047,13 +3047,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>92.1890546718882</v>
+        <v>88.41717999217197</v>
       </c>
     </row>
     <row r="10">
@@ -3061,13 +3061,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>9.395325529641976</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>105.7685889170301</v>
+        <v>100.7862193179776</v>
       </c>
     </row>
     <row r="11">
@@ -3075,13 +3075,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.996335051090269</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>10.30638739918301</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="D11" t="n">
-        <v>114.0810467288878</v>
+        <v>112.1263870497324</v>
       </c>
     </row>
     <row r="12">
@@ -3089,13 +3089,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.027750977626168</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>115.426041083706</v>
+        <v>117.3787372674529</v>
       </c>
     </row>
     <row r="13">
@@ -3103,13 +3103,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.804894248762142</v>
+        <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D13" t="n">
-        <v>117.593740014683</v>
+        <v>121.496187139064</v>
       </c>
     </row>
     <row r="14">
@@ -3117,13 +3117,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.37488875430204</v>
+        <v>7.989462817160544</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>115.5399238173986</v>
+        <v>122.3002385088422</v>
       </c>
     </row>
     <row r="15">
@@ -3134,10 +3134,10 @@
         <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>110.3680769114264</v>
+        <v>123.9849175693297</v>
       </c>
     </row>
     <row r="16">
@@ -3145,13 +3145,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>92.99605128477911</v>
+        <v>122.7547876959084</v>
       </c>
     </row>
     <row r="17">
@@ -3159,13 +3159,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>74.13864138160638</v>
+        <v>106.2496452921111</v>
       </c>
     </row>
     <row r="18">
@@ -3173,13 +3173,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>21.93715245139498</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>46.014514898048</v>
+        <v>92.56408229491051</v>
       </c>
     </row>
     <row r="19">
@@ -3190,10 +3190,10 @@
         <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>19.85977430920873</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>18.05434028109884</v>
+        <v>75.82822918061514</v>
       </c>
     </row>
     <row r="20">
@@ -3201,13 +3201,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>4.03498306445439</v>
+        <v>8.06996612890878</v>
       </c>
       <c r="C20" t="n">
-        <v>8.06996612890878</v>
+        <v>21.51990967709008</v>
       </c>
       <c r="D20" t="n">
-        <v>2.017491532227195</v>
+        <v>53.12727701531613</v>
       </c>
     </row>
     <row r="21">
@@ -3215,13 +3215,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>36.71864893903717</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>55.99593963203169</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>11.01559468171115</v>
       </c>
     </row>
   </sheetData>
@@ -3260,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.65552972899638</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="C2" t="n">
-        <v>3.429244730934109</v>
+        <v>4.706498494159209</v>
       </c>
       <c r="D2" t="n">
-        <v>91.1523290962036</v>
+        <v>127.2688636400352</v>
       </c>
     </row>
     <row r="3">
@@ -3274,13 +3274,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>44.71369918992098</v>
+        <v>50.31456984264904</v>
       </c>
       <c r="C3" t="n">
-        <v>11.6042578641973</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="D3" t="n">
-        <v>68.09892950508001</v>
+        <v>90.93928984438205</v>
       </c>
     </row>
     <row r="4">
@@ -3288,13 +3288,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>65.62590703808229</v>
+        <v>72.68369128391261</v>
       </c>
       <c r="C4" t="n">
-        <v>13.71992416684918</v>
+        <v>15.6981457909065</v>
       </c>
       <c r="D4" t="n">
-        <v>65.97050048227291</v>
+        <v>68.08911202803753</v>
       </c>
     </row>
     <row r="5">
@@ -3302,13 +3302,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.26292242941824</v>
+        <v>74.17103905584653</v>
       </c>
       <c r="C5" t="n">
-        <v>8.320311793491719</v>
+        <v>9.3266031903447</v>
       </c>
       <c r="D5" t="n">
-        <v>39.34353924769093</v>
+        <v>48.15472489330606</v>
       </c>
     </row>
     <row r="6">
@@ -3316,13 +3316,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.97246397768143</v>
+        <v>66.41523219229674</v>
       </c>
       <c r="C6" t="n">
-        <v>5.474225198880216</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="D6" t="n">
-        <v>48.5434969841878</v>
+        <v>46.4504108787336</v>
       </c>
     </row>
     <row r="7">
@@ -3330,13 +3330,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.17044855210722</v>
+        <v>28.62579956042849</v>
       </c>
       <c r="C7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="D7" t="n">
-        <v>61.26400198811371</v>
+        <v>57.49114556069321</v>
       </c>
     </row>
     <row r="8">
@@ -3344,13 +3344,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.920699420134261</v>
       </c>
       <c r="C8" t="n">
-        <v>7.009678608322226</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>76.18853058807372</v>
+        <v>71.76575718044184</v>
       </c>
     </row>
     <row r="9">
@@ -3358,13 +3358,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>91.41249223782897</v>
+        <v>86.97499261463339</v>
       </c>
     </row>
     <row r="10">
@@ -3372,13 +3372,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>9.537678946757763</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>105.3415286656828</v>
+        <v>99.36268514681969</v>
       </c>
     </row>
     <row r="11">
@@ -3386,13 +3386,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>10.48408373365169</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="D11" t="n">
-        <v>112.6594760531384</v>
+        <v>110.5271200395144</v>
       </c>
     </row>
     <row r="12">
@@ -3400,13 +3400,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.461683462903258</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49921085984289</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>113.6903111425976</v>
+        <v>115.8599735689831</v>
       </c>
     </row>
     <row r="13">
@@ -3417,10 +3417,10 @@
         <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D13" t="n">
-        <v>114.9921085984289</v>
+        <v>120.9758608558132</v>
       </c>
     </row>
     <row r="14">
@@ -3428,13 +3428,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.682175785731292</v>
+        <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>111.8524794402476</v>
+        <v>120.4565163202666</v>
       </c>
     </row>
     <row r="15">
@@ -3442,13 +3442,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>104.634670318625</v>
+        <v>122.1932280090792</v>
       </c>
     </row>
     <row r="16">
@@ -3456,13 +3456,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>7.439684102782329</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>85.55636718199678</v>
+        <v>120.6882087784689</v>
       </c>
     </row>
     <row r="17">
@@ -3470,13 +3470,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>64.69422846675207</v>
+        <v>105.3052040006256</v>
       </c>
     </row>
     <row r="18">
@@ -3484,13 +3484,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>20.86704745376595</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>35.84851742057228</v>
+        <v>91.49397729728149</v>
       </c>
     </row>
     <row r="19">
@@ -3498,13 +3498,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>7.221736112439537</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>11.4344155113626</v>
+        <v>75.22641783791184</v>
       </c>
     </row>
     <row r="20">
@@ -3512,13 +3512,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.68998870963626</v>
+        <v>7.397468951499714</v>
       </c>
       <c r="C20" t="n">
-        <v>4.707480241863455</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="D20" t="n">
-        <v>0.672497177409065</v>
+        <v>53.12727701531613</v>
       </c>
     </row>
     <row r="21">
@@ -3526,13 +3526,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>41.00928429022514</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>61.9907785782473</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>13.35186000146865</v>
       </c>
     </row>
   </sheetData>
@@ -3571,13 +3571,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.36184829670635</v>
+        <v>22.72255061479242</v>
       </c>
       <c r="C2" t="n">
-        <v>2.797980957103409</v>
+        <v>3.98000519301657</v>
       </c>
       <c r="D2" t="n">
-        <v>114.2067104350315</v>
+        <v>163.5797842293078</v>
       </c>
     </row>
     <row r="3">
@@ -3585,13 +3585,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54.48699758569798</v>
+        <v>58.84104865403258</v>
       </c>
       <c r="C3" t="n">
-        <v>11.83987731321653</v>
+        <v>14.82439033412684</v>
       </c>
       <c r="D3" t="n">
-        <v>80.98927686184062</v>
+        <v>108.3898552873691</v>
       </c>
     </row>
     <row r="4">
@@ -3599,13 +3599,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>91.3555508709827</v>
+        <v>97.71138550827655</v>
       </c>
       <c r="C4" t="n">
-        <v>16.77021428394402</v>
+        <v>19.2844701545201</v>
       </c>
       <c r="D4" t="n">
-        <v>68.22950194974482</v>
+        <v>73.43669177306991</v>
       </c>
     </row>
     <row r="5">
@@ -3613,13 +3613,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>99.47558613280809</v>
+        <v>104.6052178874977</v>
       </c>
       <c r="C5" t="n">
-        <v>11.78097245096173</v>
+        <v>13.15541923690726</v>
       </c>
       <c r="D5" t="n">
-        <v>40.64435495581795</v>
+        <v>50.19185137961819</v>
       </c>
     </row>
     <row r="6">
@@ -3627,13 +3627,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>97.93227874173209</v>
+        <v>96.56372244201204</v>
       </c>
       <c r="C6" t="n">
-        <v>6.923284810348508</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="D6" t="n">
-        <v>49.1875234781737</v>
+        <v>47.01393406097126</v>
       </c>
     </row>
     <row r="7">
@@ -3641,13 +3641,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>68.33062196328224</v>
+        <v>71.44472568115313</v>
       </c>
       <c r="C7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="D7" t="n">
-        <v>61.02445554827749</v>
+        <v>56.89227946110266</v>
       </c>
     </row>
     <row r="8">
@@ -3655,13 +3655,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.19731559302038</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="C8" t="n">
-        <v>7.093127163183205</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>75.77128781376882</v>
+        <v>70.68092596724911</v>
       </c>
     </row>
     <row r="9">
@@ -3669,13 +3669,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>3.993749660876023</v>
       </c>
       <c r="C9" t="n">
-        <v>8.320311793491715</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>91.52342972840887</v>
+        <v>85.64374272767472</v>
       </c>
     </row>
     <row r="10">
@@ -3683,13 +3683,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>9.680032363873552</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>103.7756410774091</v>
+        <v>97.9391509756618</v>
       </c>
     </row>
     <row r="11">
@@ -3697,13 +3697,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.529424054496287</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>10.66178006812036</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="D11" t="n">
-        <v>111.0602090429204</v>
+        <v>109.9940310361084</v>
       </c>
     </row>
     <row r="12">
@@ -3711,13 +3711,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.895615948180348</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
-        <v>11.71617710248143</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>111.9545812014893</v>
+        <v>114.1242436278747</v>
       </c>
     </row>
     <row r="13">
@@ -3725,13 +3725,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.585383673638358</v>
+        <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="D13" t="n">
-        <v>112.1303140405495</v>
+        <v>119.1547188644354</v>
       </c>
     </row>
     <row r="14">
@@ -3739,13 +3739,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.682175785731292</v>
+        <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>107.8577480316673</v>
+        <v>118.9200811631204</v>
       </c>
     </row>
     <row r="15">
@@ -3753,13 +3753,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>98.54292581377359</v>
+        <v>120.4015384488288</v>
       </c>
     </row>
     <row r="16">
@@ -3770,10 +3770,10 @@
         <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>78.11668307921445</v>
+        <v>119.0349456445173</v>
       </c>
     </row>
     <row r="17">
@@ -3781,13 +3781,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>54.77759490615504</v>
+        <v>104.3607627091402</v>
       </c>
     </row>
     <row r="18">
@@ -3795,13 +3795,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>27.28767743954009</v>
+        <v>90.42387229965247</v>
       </c>
     </row>
     <row r="19">
@@ -3809,13 +3809,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63803819676919</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>6.619924769736241</v>
+        <v>74.62460649520854</v>
       </c>
     </row>
     <row r="20">
@@ -3823,13 +3823,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>2.68998870963626</v>
+        <v>20.17491532227195</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>53.12727701531613</v>
       </c>
     </row>
     <row r="21">
@@ -3837,13 +3837,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>44.50791736072754</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>67.25640845621051</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>15.82503728381424</v>
       </c>
     </row>
   </sheetData>
@@ -3882,13 +3882,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.59304203328985</v>
+        <v>33.93901813581223</v>
       </c>
       <c r="C2" t="n">
-        <v>2.13628300444106</v>
+        <v>3.145519644406781</v>
       </c>
       <c r="D2" t="n">
-        <v>118.9514970896563</v>
+        <v>172.9780550020625</v>
       </c>
     </row>
     <row r="3">
@@ -3896,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>77.00828992111981</v>
+        <v>77.84768420825083</v>
       </c>
       <c r="C3" t="n">
-        <v>11.32445976848696</v>
+        <v>14.72621556370216</v>
       </c>
       <c r="D3" t="n">
-        <v>97.47772955466581</v>
+        <v>131.5640098461151</v>
       </c>
     </row>
     <row r="4">
@@ -3910,13 +3910,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>111.878004880558</v>
+        <v>116.102465251932</v>
       </c>
       <c r="C4" t="n">
-        <v>19.37380919560656</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D4" t="n">
-        <v>71.61162279087509</v>
+        <v>80.49447601890023</v>
       </c>
     </row>
     <row r="5">
@@ -3924,13 +3924,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>136.5856493533375</v>
+        <v>140.119941088626</v>
       </c>
       <c r="C5" t="n">
-        <v>15.46252634188727</v>
+        <v>17.20512851692536</v>
       </c>
       <c r="D5" t="n">
-        <v>41.99425804915732</v>
+        <v>52.54804586981054</v>
       </c>
     </row>
     <row r="6">
@@ -3938,13 +3938,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>134.4405306195582</v>
+        <v>135.8090869192783</v>
       </c>
       <c r="C6" t="n">
-        <v>9.016370915802709</v>
+        <v>9.94215900090745</v>
       </c>
       <c r="D6" t="n">
-        <v>49.87180162803373</v>
+        <v>47.69821221083129</v>
       </c>
     </row>
     <row r="7">
@@ -3952,13 +3952,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>111.329207913884</v>
+        <v>110.0117024947848</v>
       </c>
       <c r="C7" t="n">
-        <v>6.707300315414209</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="D7" t="n">
-        <v>60.78490910844126</v>
+        <v>56.35329997147116</v>
       </c>
     </row>
     <row r="8">
@@ -3966,13 +3966,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60.4167537193487</v>
+        <v>67.67677799225388</v>
       </c>
       <c r="C8" t="n">
-        <v>7.34347282776614</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="D8" t="n">
-        <v>75.35404503946393</v>
+        <v>69.67954330891736</v>
       </c>
     </row>
     <row r="9">
@@ -3980,13 +3980,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.30624853046277</v>
+        <v>21.41093568191868</v>
       </c>
       <c r="C9" t="n">
-        <v>8.431249284071605</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>91.52342972840887</v>
+        <v>85.08905527477528</v>
       </c>
     </row>
     <row r="10">
@@ -3994,13 +3994,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>9.82238578098934</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>102.2097534891354</v>
+        <v>96.37326338738815</v>
       </c>
     </row>
     <row r="11">
@@ -4008,13 +4008,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.529424054496287</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>10.83947640258903</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="D11" t="n">
-        <v>109.4609420327023</v>
+        <v>108.2170676914216</v>
       </c>
     </row>
     <row r="12">
@@ -4022,13 +4022,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.112582190818895</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
-        <v>11.93314334511998</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>110.0018850177424</v>
+        <v>112.6054799294049</v>
       </c>
     </row>
     <row r="13">
@@ -4036,13 +4036,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.845546815263763</v>
+        <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="D13" t="n">
-        <v>109.26851948267</v>
+        <v>117.3335768730576</v>
       </c>
     </row>
     <row r="14">
@@ -4050,13 +4050,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.989462817160544</v>
+        <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>103.5557295916578</v>
+        <v>117.3836460059741</v>
       </c>
     </row>
     <row r="15">
@@ -4064,13 +4064,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>92.45118130892213</v>
+        <v>118.6098488885784</v>
       </c>
     </row>
     <row r="16">
@@ -4081,10 +4081,10 @@
         <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>70.67699897643212</v>
+        <v>117.3816825105656</v>
       </c>
     </row>
     <row r="17">
@@ -4092,13 +4092,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>45.33318199130072</v>
+        <v>103.4163214176548</v>
       </c>
     </row>
     <row r="18">
@@ -4109,10 +4109,10 @@
         <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>19.79694245613693</v>
+        <v>89.35376730202346</v>
       </c>
     </row>
     <row r="19">
@@ -4120,13 +4120,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>9.628981483252716</v>
+        <v>17.45252893839555</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>74.62460649520854</v>
       </c>
     </row>
     <row r="20">
@@ -4134,13 +4134,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>1.34499435481813</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>52.45477983790707</v>
       </c>
     </row>
     <row r="21">
@@ -4148,13 +4148,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>47.07717691904259</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>72.66259915765269</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>18.42150401179927</v>
       </c>
     </row>
   </sheetData>

--- a/4.1 Myrmidon Happy reef/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.5053476924424</v>
+        <v>42.06592563156733</v>
       </c>
       <c r="C2" t="n">
-        <v>3.700207097306228</v>
+        <v>4.322635141798706</v>
       </c>
       <c r="D2" t="n">
-        <v>155.7032223981356</v>
+        <v>149.8068456864293</v>
       </c>
     </row>
     <row r="3">
@@ -786,13 +786,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>110.7607759931252</v>
+        <v>113.0531568825415</v>
       </c>
       <c r="C3" t="n">
-        <v>13.83773389135879</v>
+        <v>16.48845269282518</v>
       </c>
       <c r="D3" t="n">
-        <v>154.5810847721815</v>
+        <v>149.5005404027043</v>
       </c>
     </row>
     <row r="4">
@@ -800,13 +800,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>146.9627225872263</v>
+        <v>149.0813341329909</v>
       </c>
       <c r="C4" t="n">
-        <v>24.24916829489622</v>
+        <v>30.32422308877548</v>
       </c>
       <c r="D4" t="n">
-        <v>89.82402445235768</v>
+        <v>88.71366779885453</v>
       </c>
     </row>
     <row r="5">
@@ -814,13 +814,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>169.0324109786946</v>
+        <v>174.3829359668397</v>
       </c>
       <c r="C5" t="n">
-        <v>21.15666302651877</v>
+        <v>26.28629478120835</v>
       </c>
       <c r="D5" t="n">
-        <v>55.34602682691395</v>
+        <v>55.61600744558182</v>
       </c>
     </row>
     <row r="6">
@@ -828,13 +828,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>179.3211269192012</v>
+        <v>188.7400143937451</v>
       </c>
       <c r="C6" t="n">
-        <v>13.00128484734051</v>
+        <v>14.97361598517235</v>
       </c>
       <c r="D6" t="n">
-        <v>48.98626519880311</v>
+        <v>47.69821221083129</v>
       </c>
     </row>
     <row r="7">
@@ -842,13 +842,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155.3458662337898</v>
+        <v>157.741330632152</v>
       </c>
       <c r="C7" t="n">
-        <v>8.204465564390594</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="D7" t="n">
-        <v>55.75443387188061</v>
+        <v>55.69454726192155</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111.4038207394068</v>
+        <v>106.730701667192</v>
       </c>
       <c r="C8" t="n">
-        <v>7.009678608322226</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="D8" t="n">
-        <v>68.59471209572465</v>
+        <v>68.92850631516855</v>
       </c>
     </row>
     <row r="9">
@@ -870,13 +870,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57.90937008270233</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="C9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="D9" t="n">
-        <v>83.6468678972367</v>
+        <v>85.75468021825461</v>
       </c>
     </row>
     <row r="10">
@@ -884,10 +884,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16.79770321966293</v>
+        <v>13.6659280431156</v>
       </c>
       <c r="C10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
         <v>94.80737579911448</v>
@@ -898,13 +898,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.863979037466197</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>9.773298395776996</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>106.4401043467349</v>
+        <v>105.5516226743916</v>
       </c>
     </row>
     <row r="12">
@@ -912,13 +912,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>111.0867162309351</v>
+        <v>111.5206487162122</v>
       </c>
     </row>
     <row r="13">
@@ -929,10 +929,10 @@
         <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6666888066416</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>115.5124348816797</v>
+        <v>114.7319454568035</v>
       </c>
     </row>
     <row r="14">
@@ -940,13 +940,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8.296749848589794</v>
+        <v>7.989462817160544</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="D14" t="n">
-        <v>115.8472108488279</v>
+        <v>116.4617849116864</v>
       </c>
     </row>
     <row r="15">
@@ -954,13 +954,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>11.10847527355266</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>116.818159328328</v>
+        <v>113.5931181198772</v>
       </c>
     </row>
     <row r="16">
@@ -968,13 +968,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
         <v>11.5728419376614</v>
       </c>
       <c r="D16" t="n">
-        <v>115.728419376614</v>
+        <v>113.6618404591745</v>
       </c>
     </row>
     <row r="17">
@@ -982,13 +982,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
         <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>103.4163214176548</v>
+        <v>99.63855625171304</v>
       </c>
     </row>
     <row r="18">
@@ -996,13 +996,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
         <v>14.98146996680633</v>
       </c>
       <c r="D18" t="n">
-        <v>88.28366230439441</v>
+        <v>88.81871480320895</v>
       </c>
     </row>
     <row r="19">
@@ -1010,13 +1010,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>73.42098380980195</v>
+        <v>68.00468172547231</v>
       </c>
     </row>
     <row r="20">
@@ -1030,7 +1030,7 @@
         <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>51.78228266049801</v>
+        <v>47.07480241863455</v>
       </c>
     </row>
     <row r="21">
@@ -1038,13 +1038,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>48.59483127677039</v>
+        <v>22.03304917197059</v>
       </c>
       <c r="C21" t="n">
-        <v>77.11788441748344</v>
+        <v>44.06609834394117</v>
       </c>
       <c r="D21" t="n">
-        <v>20.07177813605733</v>
+        <v>7.050575735030587</v>
       </c>
     </row>
   </sheetData>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>53.53666580798706</v>
+        <v>54.80115685105696</v>
       </c>
       <c r="C2" t="n">
-        <v>3.566689409528662</v>
+        <v>4.116468123906875</v>
       </c>
       <c r="D2" t="n">
-        <v>131.7417061805837</v>
+        <v>126.738719879742</v>
       </c>
     </row>
     <row r="3">
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>137.3563213011712</v>
+        <v>140.203389643487</v>
       </c>
       <c r="C3" t="n">
-        <v>13.55302705712722</v>
+        <v>16.26265072084841</v>
       </c>
       <c r="D3" t="n">
-        <v>173.6024465419635</v>
+        <v>166.3031523608884</v>
       </c>
     </row>
     <row r="4">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>198.5496374545792</v>
+        <v>204.841658491097</v>
       </c>
       <c r="C4" t="n">
-        <v>25.29571134762332</v>
+        <v>31.26866438026091</v>
       </c>
       <c r="D4" t="n">
-        <v>98.20913159432968</v>
+        <v>100.4043194610256</v>
       </c>
     </row>
     <row r="5">
@@ -1125,13 +1125,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>207.6641831408066</v>
+        <v>213.3828635180443</v>
       </c>
       <c r="C5" t="n">
-        <v>24.69095476180729</v>
+        <v>30.99868376159304</v>
       </c>
       <c r="D5" t="n">
-        <v>57.62859023928778</v>
+        <v>57.80039608753097</v>
       </c>
     </row>
     <row r="6">
@@ -1139,13 +1139,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>218.1237231818521</v>
+        <v>229.0721735796126</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D6" t="n">
-        <v>49.54978838104078</v>
+        <v>48.3422387048172</v>
       </c>
     </row>
     <row r="7">
@@ -1153,13 +1153,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204.6924328400515</v>
+        <v>211.1601867156295</v>
       </c>
       <c r="C7" t="n">
-        <v>9.881290643244144</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="D7" t="n">
-        <v>55.27534099220816</v>
+        <v>55.15556777229006</v>
       </c>
     </row>
     <row r="8">
@@ -1167,13 +1167,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159.2198426747477</v>
+        <v>156.8832831386403</v>
       </c>
       <c r="C8" t="n">
-        <v>7.593818492349078</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="D8" t="n">
-        <v>67.5098808825319</v>
+        <v>67.84367510197582</v>
       </c>
     </row>
     <row r="9">
@@ -1181,13 +1181,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100.6203039559598</v>
+        <v>89.08280493565131</v>
       </c>
       <c r="C9" t="n">
-        <v>7.765624340592267</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="D9" t="n">
-        <v>82.20468051969816</v>
+        <v>85.08905527477528</v>
       </c>
     </row>
     <row r="10">
@@ -1195,13 +1195,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44.69897297435728</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="C10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>93.3838416279566</v>
+        <v>93.24148821084083</v>
       </c>
     </row>
     <row r="11">
@@ -1209,13 +1209,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12.9718324162131</v>
+        <v>10.66178006812036</v>
       </c>
       <c r="C11" t="n">
         <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>104.6631410020482</v>
+        <v>103.7746593297048</v>
       </c>
     </row>
     <row r="12">
@@ -1223,13 +1223,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>109.5679525324653</v>
+        <v>109.7849187751038</v>
       </c>
     </row>
     <row r="13">
@@ -1237,13 +1237,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.804894248762142</v>
+        <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6666888066416</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>113.6912928903019</v>
+        <v>112.9108034654257</v>
       </c>
     </row>
     <row r="14">
@@ -1251,13 +1251,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8.296749848589794</v>
+        <v>7.989462817160544</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="D14" t="n">
-        <v>114.3107756916816</v>
+        <v>114.6180627231109</v>
       </c>
     </row>
     <row r="15">
@@ -1265,13 +1265,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
         <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>116.1014835042278</v>
+        <v>112.876442295777</v>
       </c>
     </row>
     <row r="16">
@@ -1279,13 +1279,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
         <v>11.15952615417349</v>
       </c>
       <c r="D16" t="n">
-        <v>113.6618404591745</v>
+        <v>111.5952615417349</v>
       </c>
     </row>
     <row r="17">
@@ -1293,13 +1293,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
         <v>12.74995743505333</v>
       </c>
       <c r="D17" t="n">
-        <v>101.9996594804266</v>
+        <v>98.2218943144849</v>
       </c>
     </row>
     <row r="18">
@@ -1307,7 +1307,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
         <v>14.44641746799181</v>
@@ -1321,13 +1321,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
         <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>72.21736112439537</v>
+        <v>66.80105904006572</v>
       </c>
     </row>
     <row r="20">
@@ -1335,13 +1335,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
         <v>18.15742379004475</v>
       </c>
       <c r="D20" t="n">
-        <v>51.10978548308893</v>
+        <v>47.07480241863455</v>
       </c>
     </row>
     <row r="21">
@@ -1349,13 +1349,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>48.94715057699965</v>
+        <v>21.45409784387543</v>
       </c>
       <c r="C21" t="n">
-        <v>81.5785842949994</v>
+        <v>44.6960371747405</v>
       </c>
       <c r="D21" t="n">
-        <v>21.75428914533317</v>
+        <v>7.151365947958479</v>
       </c>
     </row>
   </sheetData>
@@ -1394,13 +1394,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>64.23673403657305</v>
+        <v>65.94988378048373</v>
       </c>
       <c r="C2" t="n">
-        <v>2.747911824186823</v>
+        <v>3.169081589308704</v>
       </c>
       <c r="D2" t="n">
-        <v>159.1805727665778</v>
+        <v>153.1555871056152</v>
       </c>
     </row>
     <row r="3">
@@ -1408,13 +1408,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>171.4131491614931</v>
+        <v>176.3071614671634</v>
       </c>
       <c r="C3" t="n">
-        <v>13.22414157620454</v>
+        <v>15.75705065316131</v>
       </c>
       <c r="D3" t="n">
-        <v>181.0686378327605</v>
+        <v>173.5386329411874</v>
       </c>
     </row>
     <row r="4">
@@ -1422,13 +1422,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>246.5119397978528</v>
+        <v>255.5607083878957</v>
       </c>
       <c r="C4" t="n">
-        <v>25.89555919491812</v>
+        <v>31.80469862677967</v>
       </c>
       <c r="D4" t="n">
-        <v>107.8322225913569</v>
+        <v>109.1340200471882</v>
       </c>
     </row>
     <row r="5">
@@ -1436,13 +1436,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>267.1826377107695</v>
+        <v>277.2455516792993</v>
       </c>
       <c r="C5" t="n">
-        <v>27.83254741539708</v>
+        <v>34.80295611554943</v>
       </c>
       <c r="D5" t="n">
-        <v>60.35294011857268</v>
+        <v>60.67200812245289</v>
       </c>
     </row>
     <row r="6">
@@ -1450,13 +1450,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>264.6546373723339</v>
+        <v>275.0798162437308</v>
       </c>
       <c r="C6" t="n">
-        <v>19.80381469006666</v>
+        <v>23.90948358922682</v>
       </c>
       <c r="D6" t="n">
-        <v>50.2340665309008</v>
+        <v>49.10702016642546</v>
       </c>
     </row>
     <row r="7">
@@ -1464,13 +1464,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>247.8107920105714</v>
+        <v>260.0875470521777</v>
       </c>
       <c r="C7" t="n">
-        <v>11.97732199181109</v>
+        <v>13.05528097107408</v>
       </c>
       <c r="D7" t="n">
-        <v>54.85613472249477</v>
+        <v>54.67647489261761</v>
       </c>
     </row>
     <row r="8">
@@ -1478,13 +1478,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>210.2903582496668</v>
+        <v>210.0400125850838</v>
       </c>
       <c r="C8" t="n">
-        <v>8.344855486097888</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="D8" t="n">
-        <v>66.50849822420017</v>
+        <v>67.42643232767094</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1492,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>147.2140499995134</v>
+        <v>135.7874884697848</v>
       </c>
       <c r="C9" t="n">
-        <v>7.987499321752047</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="D9" t="n">
-        <v>80.76249314215958</v>
+        <v>83.53593040665682</v>
       </c>
     </row>
     <row r="10">
@@ -1506,13 +1506,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>81.42615459023047</v>
+        <v>65.62492529037804</v>
       </c>
       <c r="C10" t="n">
         <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>91.96030745679873</v>
+        <v>91.81795403968295</v>
       </c>
     </row>
     <row r="11">
@@ -1520,13 +1520,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31.62994753542373</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="C11" t="n">
         <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>102.8861776573615</v>
+        <v>101.9976959850181</v>
       </c>
     </row>
     <row r="12">
@@ -1534,13 +1534,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.41437964665016</v>
+        <v>9.112582190818895</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>9.980447161373073</v>
       </c>
       <c r="D12" t="n">
-        <v>109.1340200471882</v>
+        <v>108.0491888339954</v>
       </c>
     </row>
     <row r="13">
@@ -1548,13 +1548,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.284567965511334</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6666888066416</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>111.8701508989241</v>
+        <v>111.0896614740478</v>
       </c>
     </row>
     <row r="14">
@@ -1565,10 +1565,10 @@
         <v>7.989462817160544</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="D14" t="n">
-        <v>112.4670535031061</v>
+        <v>113.6962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -1576,13 +1576,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.883434065101886</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="D15" t="n">
-        <v>113.9514560319273</v>
+        <v>110.7264148234765</v>
       </c>
     </row>
     <row r="16">
@@ -1590,13 +1590,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
-        <v>10.74621037068559</v>
+        <v>11.15952615417349</v>
       </c>
       <c r="D16" t="n">
-        <v>111.5952615417349</v>
+        <v>109.5286826242954</v>
       </c>
     </row>
     <row r="17">
@@ -1604,13 +1604,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
         <v>12.27773678931061</v>
       </c>
       <c r="D17" t="n">
-        <v>100.5829975431985</v>
+        <v>96.80523237725674</v>
       </c>
     </row>
     <row r="18">
@@ -1618,13 +1618,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
         <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>86.14345230913638</v>
+        <v>85.60839981032187</v>
       </c>
     </row>
     <row r="19">
@@ -1632,13 +1632,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
         <v>15.64709491028566</v>
       </c>
       <c r="D19" t="n">
-        <v>71.01373843898878</v>
+        <v>66.19924769736242</v>
       </c>
     </row>
     <row r="20">
@@ -1646,13 +1646,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
         <v>17.48492661263569</v>
       </c>
       <c r="D20" t="n">
-        <v>50.43728830567987</v>
+        <v>46.40230524122548</v>
       </c>
     </row>
     <row r="21">
@@ -1660,13 +1660,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>49.14494411637857</v>
+        <v>20.82620170460968</v>
       </c>
       <c r="C21" t="n">
-        <v>84.88672165556298</v>
+        <v>45.27435153176018</v>
       </c>
       <c r="D21" t="n">
-        <v>23.45554151008977</v>
+        <v>7.243896245081629</v>
       </c>
     </row>
   </sheetData>
@@ -1705,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.710024574348697</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C2" t="n">
-        <v>4.299073196896783</v>
+        <v>5.258240703945916</v>
       </c>
       <c r="D2" t="n">
-        <v>16.10458934046468</v>
+        <v>15.6814560799343</v>
       </c>
     </row>
     <row r="3">
@@ -1733,10 +1733,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7657632093125121</v>
+        <v>0.7785259294677207</v>
       </c>
       <c r="C4" t="n">
-        <v>2.271764187627119</v>
+        <v>2.297289627937536</v>
       </c>
       <c r="D4" t="n">
         <v>64.26029598147497</v>
@@ -1750,10 +1750,10 @@
         <v>1.84077694546277</v>
       </c>
       <c r="C5" t="n">
-        <v>2.896155727528091</v>
+        <v>2.871612034921921</v>
       </c>
       <c r="D5" t="n">
-        <v>34.53297549688156</v>
+        <v>34.82749980815561</v>
       </c>
     </row>
     <row r="6">
@@ -1761,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.857867567062466</v>
+        <v>2.898119222936585</v>
       </c>
       <c r="C6" t="n">
-        <v>3.703152340418969</v>
+        <v>3.743403996293088</v>
       </c>
       <c r="D6" t="n">
-        <v>45.00135126726531</v>
+        <v>44.55858305264999</v>
       </c>
     </row>
     <row r="7">
@@ -1775,10 +1775,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.832743037379548</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="D7" t="n">
         <v>61.6832082578271</v>
@@ -1792,7 +1792,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>6.508987279156353</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="D8" t="n">
         <v>77.4402589109884</v>
@@ -1806,10 +1806,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>7.654686850012379</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>94.2968669929061</v>
+        <v>95.18436691754523</v>
       </c>
     </row>
     <row r="10">
@@ -1820,10 +1820,10 @@
         <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>8.683558444063038</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>106.6227094197249</v>
+        <v>106.4803560026091</v>
       </c>
     </row>
     <row r="11">
@@ -1851,7 +1851,7 @@
         <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>123.4537920613322</v>
+        <v>123.2368258186936</v>
       </c>
     </row>
     <row r="13">
@@ -1865,7 +1865,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>127.7401025380738</v>
+        <v>127.4799393964483</v>
       </c>
     </row>
     <row r="14">
@@ -1879,7 +1879,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>127.2168310117102</v>
+        <v>128.1386921059979</v>
       </c>
     </row>
     <row r="15">
@@ -1893,7 +1893,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>129.359986250081</v>
+        <v>129.0016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -1907,7 +1907,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>129.3678402317149</v>
+        <v>127.7145770977633</v>
       </c>
     </row>
     <row r="17">
@@ -1935,7 +1935,7 @@
         <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>96.84450228542661</v>
+        <v>97.37955478424112</v>
       </c>
     </row>
     <row r="19">
@@ -1949,7 +1949,7 @@
         <v>21.66520833731861</v>
       </c>
       <c r="D19" t="n">
-        <v>78.23547455142831</v>
+        <v>77.63366320872503</v>
       </c>
     </row>
     <row r="20">
@@ -1963,7 +1963,7 @@
         <v>24.20989838672634</v>
       </c>
       <c r="D20" t="n">
-        <v>53.12727701531613</v>
+        <v>51.78228266049801</v>
       </c>
     </row>
     <row r="21">
@@ -1971,13 +1971,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17.12765163770884</v>
+        <v>13.71222416084723</v>
       </c>
       <c r="C21" t="n">
-        <v>33.47677365552183</v>
+        <v>29.709819015169</v>
       </c>
       <c r="D21" t="n">
-        <v>2.33558885968757</v>
+        <v>0.7617902311581793</v>
       </c>
     </row>
   </sheetData>
@@ -2016,13 +2016,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.813909904549611</v>
+        <v>5.941537106101696</v>
       </c>
       <c r="C2" t="n">
-        <v>4.895975801078843</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="D2" t="n">
-        <v>60.24102088028854</v>
+        <v>58.25396352689299</v>
       </c>
     </row>
     <row r="3">
@@ -2030,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.73679380427062</v>
+        <v>12.15894531709675</v>
       </c>
       <c r="C3" t="n">
-        <v>4.609305471438775</v>
+        <v>5.532148313430777</v>
       </c>
       <c r="D3" t="n">
-        <v>31.38156536624929</v>
+        <v>31.27848185730338</v>
       </c>
     </row>
     <row r="4">
@@ -2044,10 +2044,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2807798434145877</v>
+        <v>0.2935425635697963</v>
       </c>
       <c r="C4" t="n">
-        <v>2.067560665143783</v>
+        <v>2.0930861054542</v>
       </c>
       <c r="D4" t="n">
         <v>62.55009148067703</v>
@@ -2058,13 +2058,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.349903093339365</v>
+        <v>1.398990478551705</v>
       </c>
       <c r="C5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.117048960983624</v>
       </c>
       <c r="D5" t="n">
-        <v>38.26361677301944</v>
+        <v>38.8772090881737</v>
       </c>
     </row>
     <row r="6">
@@ -2072,13 +2072,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.777364255314227</v>
+        <v>2.817615911188346</v>
       </c>
       <c r="C6" t="n">
-        <v>3.823907308041327</v>
+        <v>3.864158963915446</v>
       </c>
       <c r="D6" t="n">
-        <v>45.12210623488766</v>
+        <v>44.19631814978292</v>
       </c>
     </row>
     <row r="7">
@@ -2086,10 +2086,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.832743037379548</v>
+        <v>3.952516257297658</v>
       </c>
       <c r="C7" t="n">
-        <v>5.030475236560656</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="D7" t="n">
         <v>60.66513588852315</v>
@@ -2100,10 +2100,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>6.508987279156353</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="D8" t="n">
         <v>76.2719791429347</v>
@@ -2117,10 +2117,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>7.654686850012379</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>92.74374212478766</v>
+        <v>94.51874197406589</v>
       </c>
     </row>
     <row r="10">
@@ -2131,10 +2131,10 @@
         <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>8.683558444063038</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>105.0568218314512</v>
+        <v>104.9144684143354</v>
       </c>
     </row>
     <row r="11">
@@ -2148,7 +2148,7 @@
         <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>117.2795807493239</v>
+        <v>117.1018844148553</v>
       </c>
     </row>
     <row r="12">
@@ -2162,7 +2162,7 @@
         <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>121.9350283628623</v>
+        <v>121.5010958775852</v>
       </c>
     </row>
     <row r="13">
@@ -2170,13 +2170,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.024404823885929</v>
+        <v>6.764241682260525</v>
       </c>
       <c r="C13" t="n">
         <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>126.1791236883213</v>
+        <v>125.6587974050705</v>
       </c>
     </row>
     <row r="14">
@@ -2187,10 +2187,10 @@
         <v>6.760314691443536</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>125.6803958545639</v>
+        <v>127.5241180431394</v>
       </c>
     </row>
     <row r="15">
@@ -2204,7 +2204,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>127.5682966898305</v>
+        <v>126.8516208657304</v>
       </c>
     </row>
     <row r="16">
@@ -2218,7 +2218,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>128.954524448227</v>
+        <v>125.6479981803238</v>
       </c>
     </row>
     <row r="17">
@@ -2226,13 +2226,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.499971623368884</v>
+        <v>8.02775097762617</v>
       </c>
       <c r="C17" t="n">
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>109.0829691665674</v>
+        <v>108.6107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2246,7 +2246,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>95.7743972877976</v>
+        <v>96.84450228542661</v>
       </c>
     </row>
     <row r="19">
@@ -2260,7 +2260,7 @@
         <v>21.06339699461531</v>
       </c>
       <c r="D19" t="n">
-        <v>77.63366320872503</v>
+        <v>76.43004052331844</v>
       </c>
     </row>
     <row r="20">
@@ -2274,7 +2274,7 @@
         <v>23.53740120931727</v>
       </c>
       <c r="D20" t="n">
-        <v>53.12727701531613</v>
+        <v>51.10978548308893</v>
       </c>
     </row>
     <row r="21">
@@ -2282,13 +2282,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22.74706248330653</v>
+        <v>16.32070008530816</v>
       </c>
       <c r="C21" t="n">
-        <v>38.99496425709691</v>
+        <v>31.86422397607783</v>
       </c>
       <c r="D21" t="n">
-        <v>4.874370532137114</v>
+        <v>1.554352389076967</v>
       </c>
     </row>
   </sheetData>
@@ -2327,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.937029278207961</v>
+        <v>6.874197425136166</v>
       </c>
       <c r="C2" t="n">
-        <v>4.329507375728434</v>
+        <v>5.278857405735099</v>
       </c>
       <c r="D2" t="n">
-        <v>66.58212930201867</v>
+        <v>64.32509132995526</v>
       </c>
     </row>
     <row r="3">
@@ -2341,13 +2341,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.33690369347268</v>
+        <v>21.05357951757285</v>
       </c>
       <c r="C3" t="n">
-        <v>8.060148651866312</v>
+        <v>9.773298395776997</v>
       </c>
       <c r="D3" t="n">
-        <v>42.77474747403353</v>
+        <v>42.20533380557038</v>
       </c>
     </row>
     <row r="4">
@@ -2355,13 +2355,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.3310132072472</v>
+        <v>21.05848825609408</v>
       </c>
       <c r="C4" t="n">
-        <v>4.288273972150068</v>
+        <v>4.849833658979244</v>
       </c>
       <c r="D4" t="n">
-        <v>61.13342954344888</v>
+        <v>61.12066682329367</v>
       </c>
     </row>
     <row r="5">
@@ -2369,13 +2369,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6381360077604269</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C5" t="n">
-        <v>3.141592653589794</v>
+        <v>3.215223731408305</v>
       </c>
       <c r="D5" t="n">
-        <v>41.45429681182157</v>
+        <v>42.36241343824987</v>
       </c>
     </row>
     <row r="6">
@@ -2383,13 +2383,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.173589417202439</v>
+        <v>2.294344384824796</v>
       </c>
       <c r="C6" t="n">
-        <v>3.984913931537804</v>
+        <v>4.065417243286043</v>
       </c>
       <c r="D6" t="n">
-        <v>45.60512610537709</v>
+        <v>44.19631814978292</v>
       </c>
     </row>
     <row r="7">
@@ -2397,13 +2397,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.772856427420492</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="D7" t="n">
-        <v>59.76683673913732</v>
+        <v>59.6470635192192</v>
       </c>
     </row>
     <row r="8">
@@ -2411,7 +2411,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
         <v>6.425538724295373</v>
@@ -2425,13 +2425,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
         <v>7.654686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>91.30155474724909</v>
+        <v>93.85311703058655</v>
       </c>
     </row>
     <row r="10">
@@ -2439,13 +2439,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
         <v>8.825911861178826</v>
       </c>
       <c r="D10" t="n">
-        <v>103.6332876602933</v>
+        <v>103.3485808260617</v>
       </c>
     </row>
     <row r="11">
@@ -2453,13 +2453,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.285549713215578</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
         <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>115.5026174046372</v>
+        <v>115.1472247356999</v>
       </c>
     </row>
     <row r="12">
@@ -2473,7 +2473,7 @@
         <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>120.4162646643925</v>
+        <v>119.7653659364769</v>
       </c>
     </row>
     <row r="13">
@@ -2481,13 +2481,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.544731107136739</v>
+        <v>7.284567965511334</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>124.6181448385689</v>
+        <v>123.8376554136927</v>
       </c>
     </row>
     <row r="14">
@@ -2495,13 +2495,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.067601722872788</v>
+        <v>6.760314691443536</v>
       </c>
       <c r="C14" t="n">
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>124.1439606974177</v>
+        <v>126.9095439802809</v>
       </c>
     </row>
     <row r="15">
@@ -2515,7 +2515,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>126.8516208657304</v>
+        <v>124.7015933934298</v>
       </c>
     </row>
     <row r="16">
@@ -2529,7 +2529,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>126.8879455307875</v>
+        <v>123.5814192628842</v>
       </c>
     </row>
     <row r="17">
@@ -2537,13 +2537,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.02775097762617</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>108.1385278750819</v>
+        <v>107.1940865835965</v>
       </c>
     </row>
     <row r="18">
@@ -2551,13 +2551,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.560839981032187</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="C18" t="n">
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>94.70429229016857</v>
+        <v>96.30944978661211</v>
       </c>
     </row>
     <row r="19">
@@ -2571,7 +2571,7 @@
         <v>20.46158565191202</v>
       </c>
       <c r="D19" t="n">
-        <v>77.03185186602173</v>
+        <v>75.22641783791184</v>
       </c>
     </row>
     <row r="20">
@@ -2585,7 +2585,7 @@
         <v>22.86490403190821</v>
       </c>
       <c r="D20" t="n">
-        <v>53.12727701531613</v>
+        <v>50.43728830567987</v>
       </c>
     </row>
     <row r="21">
@@ -2593,13 +2593,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27.95088486088985</v>
+        <v>18.2304354474503</v>
       </c>
       <c r="C21" t="n">
-        <v>44.89081507961097</v>
+        <v>34.08298801045056</v>
       </c>
       <c r="D21" t="n">
-        <v>6.775972087488448</v>
+        <v>2.377882884450039</v>
       </c>
     </row>
   </sheetData>
@@ -2638,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.48506548135594</v>
+        <v>10.56851403621691</v>
       </c>
       <c r="C2" t="n">
-        <v>6.029894399483909</v>
+        <v>7.317947387455725</v>
       </c>
       <c r="D2" t="n">
-        <v>110.27873787034</v>
+        <v>106.3988709431566</v>
       </c>
     </row>
     <row r="3">
@@ -2652,13 +2652,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.34872572365265</v>
+        <v>25.39290437034375</v>
       </c>
       <c r="C3" t="n">
-        <v>9.940195505498956</v>
+        <v>12.080405500757</v>
       </c>
       <c r="D3" t="n">
-        <v>54.57535487908019</v>
+        <v>53.51997609701487</v>
       </c>
     </row>
     <row r="4">
@@ -2666,13 +2666,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.83695743229957</v>
+        <v>40.85346721682252</v>
       </c>
       <c r="C4" t="n">
-        <v>7.785259294677207</v>
+        <v>9.189158511750145</v>
       </c>
       <c r="D4" t="n">
-        <v>61.56736202872597</v>
+        <v>62.0523453946239</v>
       </c>
     </row>
     <row r="5">
@@ -2680,13 +2680,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.45180923259857</v>
+        <v>26.04085785514665</v>
       </c>
       <c r="C5" t="n">
-        <v>4.123340357836605</v>
+        <v>4.442408361716818</v>
       </c>
       <c r="D5" t="n">
-        <v>44.57134577280519</v>
+        <v>44.25227776892498</v>
       </c>
     </row>
     <row r="6">
@@ -2694,13 +2694,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.207549676223577</v>
+        <v>1.408807955594173</v>
       </c>
       <c r="C6" t="n">
-        <v>4.145920555034281</v>
+        <v>4.22642386678252</v>
       </c>
       <c r="D6" t="n">
-        <v>45.68562941712533</v>
+        <v>44.47807974090175</v>
       </c>
     </row>
     <row r="7">
@@ -2708,13 +2708,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.114103717870883</v>
+        <v>3.353650157707104</v>
       </c>
       <c r="C7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="D7" t="n">
-        <v>58.92842419971054</v>
+        <v>58.74876436983337</v>
       </c>
     </row>
     <row r="8">
@@ -2722,10 +2722,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>6.425538724295373</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
         <v>73.93541960682728</v>
@@ -2736,13 +2736,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>89.85936736971051</v>
+        <v>93.18749208710722</v>
       </c>
     </row>
     <row r="10">
@@ -2750,13 +2750,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>102.2097534891354</v>
+        <v>101.9250466549039</v>
       </c>
     </row>
     <row r="11">
@@ -2770,7 +2770,7 @@
         <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>113.7256540599505</v>
+        <v>113.3702613910131</v>
       </c>
     </row>
     <row r="12">
@@ -2778,13 +2778,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.810784734987623</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C12" t="n">
         <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>118.8975009659227</v>
+        <v>118.0296359953685</v>
       </c>
     </row>
     <row r="13">
@@ -2792,13 +2792,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.804894248762142</v>
+        <v>7.544731107136739</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>123.0571659888165</v>
+        <v>122.0165134223148</v>
       </c>
     </row>
     <row r="14">
@@ -2806,13 +2806,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.682175785731292</v>
+        <v>7.067601722872788</v>
       </c>
       <c r="C14" t="n">
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>122.6075255402714</v>
+        <v>126.2949699174224</v>
       </c>
     </row>
     <row r="15">
@@ -2820,13 +2820,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.808420328951629</v>
       </c>
       <c r="C15" t="n">
         <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>126.1349450416302</v>
+        <v>122.5515659211293</v>
       </c>
     </row>
     <row r="16">
@@ -2840,7 +2840,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>124.821366613348</v>
+        <v>121.5148403454447</v>
       </c>
     </row>
     <row r="17">
@@ -2848,13 +2848,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>107.1940865835965</v>
+        <v>105.7774246463683</v>
       </c>
     </row>
     <row r="18">
@@ -2862,13 +2862,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>93.63418729253954</v>
+        <v>95.7743972877976</v>
       </c>
     </row>
     <row r="19">
@@ -2876,13 +2876,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
         <v>19.85977430920873</v>
       </c>
       <c r="D19" t="n">
-        <v>76.43004052331844</v>
+        <v>74.02279515250525</v>
       </c>
     </row>
     <row r="20">
@@ -2896,7 +2896,7 @@
         <v>22.19240685449914</v>
       </c>
       <c r="D20" t="n">
-        <v>53.12727701531613</v>
+        <v>49.76479112827081</v>
       </c>
     </row>
     <row r="21">
@@ -2904,13 +2904,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>32.6480931893993</v>
+        <v>19.39619430480152</v>
       </c>
       <c r="C21" t="n">
-        <v>50.29571112961514</v>
+        <v>36.36786432150285</v>
       </c>
       <c r="D21" t="n">
-        <v>8.823808970107921</v>
+        <v>3.232699050800253</v>
       </c>
     </row>
   </sheetData>
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.20883452356409</v>
+        <v>14.40714755982194</v>
       </c>
       <c r="C2" t="n">
-        <v>5.037347470490384</v>
+        <v>6.104507225006667</v>
       </c>
       <c r="D2" t="n">
-        <v>109.4511245556599</v>
+        <v>105.5486774312788</v>
       </c>
     </row>
     <row r="3">
@@ -2963,13 +2963,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>37.27205159173015</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="C3" t="n">
-        <v>12.89525609528186</v>
+        <v>15.65887588273663</v>
       </c>
       <c r="D3" t="n">
-        <v>75.71238295151402</v>
+        <v>73.82742735936014</v>
       </c>
     </row>
     <row r="4">
@@ -2977,13 +2977,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.37445645260809</v>
+        <v>52.13571183402686</v>
       </c>
       <c r="C4" t="n">
-        <v>11.52473630015331</v>
+        <v>13.80926320793563</v>
       </c>
       <c r="D4" t="n">
-        <v>64.3113468620958</v>
+        <v>64.6048894256656</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.82431788533139</v>
+        <v>55.83690067903736</v>
       </c>
       <c r="C5" t="n">
-        <v>6.234097921967248</v>
+        <v>7.093127163183206</v>
       </c>
       <c r="D5" t="n">
-        <v>46.31394794784328</v>
+        <v>46.06851102178158</v>
       </c>
     </row>
     <row r="6">
@@ -3005,13 +3005,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.82018560586937</v>
+        <v>28.41766904712818</v>
       </c>
       <c r="C6" t="n">
-        <v>4.588688769649592</v>
+        <v>4.749695393146069</v>
       </c>
       <c r="D6" t="n">
-        <v>46.00764266411829</v>
+        <v>44.88059629964295</v>
       </c>
     </row>
     <row r="7">
@@ -3019,13 +3019,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.976258128648829</v>
+        <v>2.335577788403162</v>
       </c>
       <c r="C7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="D7" t="n">
-        <v>58.14989827024283</v>
+        <v>57.9103518304066</v>
       </c>
     </row>
     <row r="8">
@@ -3033,13 +3033,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>6.508987279156353</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="D8" t="n">
-        <v>72.85058839363457</v>
+        <v>72.76713983877357</v>
       </c>
     </row>
     <row r="9">
@@ -3047,13 +3047,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>88.41717999217197</v>
+        <v>92.41092965304799</v>
       </c>
     </row>
     <row r="10">
@@ -3061,13 +3061,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>100.7862193179776</v>
+        <v>100.501512483746</v>
       </c>
     </row>
     <row r="11">
@@ -3075,13 +3075,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.285549713215578</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>9.773298395776996</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>112.1263870497324</v>
+        <v>111.5932980463264</v>
       </c>
     </row>
     <row r="12">
@@ -3095,7 +3095,7 @@
         <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>117.3787372674529</v>
+        <v>116.2939060542602</v>
       </c>
     </row>
     <row r="13">
@@ -3103,10 +3103,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.065057390387548</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
         <v>121.496187139064</v>
@@ -3117,13 +3117,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.989462817160544</v>
+        <v>7.37488875430204</v>
       </c>
       <c r="C14" t="n">
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>122.3002385088422</v>
+        <v>124.1439606974177</v>
       </c>
     </row>
     <row r="15">
@@ -3131,13 +3131,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
       <c r="C15" t="n">
         <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>123.9849175693297</v>
+        <v>120.7598763608789</v>
       </c>
     </row>
     <row r="16">
@@ -3145,13 +3145,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>122.7547876959084</v>
+        <v>119.4482614280052</v>
       </c>
     </row>
     <row r="17">
@@ -3165,7 +3165,7 @@
         <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>106.2496452921111</v>
+        <v>104.3607627091402</v>
       </c>
     </row>
     <row r="18">
@@ -3173,13 +3173,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
         <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>92.56408229491051</v>
+        <v>95.23934478898308</v>
       </c>
     </row>
     <row r="19">
@@ -3187,13 +3187,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>7.221736112439537</v>
       </c>
       <c r="C19" t="n">
         <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>75.82822918061514</v>
+        <v>72.81917246709867</v>
       </c>
     </row>
     <row r="20">
@@ -3201,13 +3201,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.06996612890878</v>
+        <v>7.397468951499714</v>
       </c>
       <c r="C20" t="n">
         <v>21.51990967709008</v>
       </c>
       <c r="D20" t="n">
-        <v>53.12727701531613</v>
+        <v>49.09229395086174</v>
       </c>
     </row>
     <row r="21">
@@ -3215,13 +3215,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>36.71864893903717</v>
+        <v>20.58910519719086</v>
       </c>
       <c r="C21" t="n">
-        <v>55.99593963203169</v>
+        <v>38.70751777071882</v>
       </c>
       <c r="D21" t="n">
-        <v>11.01559468171115</v>
+        <v>4.117821039438173</v>
       </c>
     </row>
   </sheetData>
@@ -3260,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.34217228489241</v>
+        <v>16.01721379478671</v>
       </c>
       <c r="C2" t="n">
-        <v>4.706498494159209</v>
+        <v>5.63228657926395</v>
       </c>
       <c r="D2" t="n">
-        <v>127.2688636400352</v>
+        <v>122.6428684576243</v>
       </c>
     </row>
     <row r="3">
@@ -3274,13 +3274,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>50.31456984264904</v>
+        <v>51.16869034534376</v>
       </c>
       <c r="C3" t="n">
-        <v>14.08807955594173</v>
+        <v>17.33766445699867</v>
       </c>
       <c r="D3" t="n">
-        <v>90.93928984438205</v>
+        <v>88.43583319855269</v>
       </c>
     </row>
     <row r="4">
@@ -3288,13 +3288,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>72.68369128391261</v>
+        <v>74.43218394517618</v>
       </c>
       <c r="C4" t="n">
-        <v>15.6981457909065</v>
+        <v>18.92711399017426</v>
       </c>
       <c r="D4" t="n">
-        <v>68.08911202803753</v>
+        <v>68.12740018850316</v>
       </c>
     </row>
     <row r="5">
@@ -3302,13 +3302,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.17103905584653</v>
+        <v>77.48443755767953</v>
       </c>
       <c r="C5" t="n">
-        <v>9.3266031903447</v>
+        <v>10.97103059495811</v>
       </c>
       <c r="D5" t="n">
-        <v>48.15472489330606</v>
+        <v>47.95837535245669</v>
       </c>
     </row>
     <row r="6">
@@ -3316,13 +3316,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.41523219229674</v>
+        <v>67.01900703040852</v>
       </c>
       <c r="C6" t="n">
-        <v>5.675483478250811</v>
+        <v>6.037748381117884</v>
       </c>
       <c r="D6" t="n">
-        <v>46.4504108787336</v>
+        <v>45.40386782600649</v>
       </c>
     </row>
     <row r="7">
@@ -3330,13 +3330,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.62579956042849</v>
+        <v>26.94897448157494</v>
       </c>
       <c r="C7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="D7" t="n">
-        <v>57.49114556069321</v>
+        <v>57.13182590093888</v>
       </c>
     </row>
     <row r="8">
@@ -3344,13 +3344,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.920699420134261</v>
+        <v>3.504839304161113</v>
       </c>
       <c r="C8" t="n">
-        <v>6.508987279156353</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="D8" t="n">
-        <v>71.76575718044184</v>
+        <v>72.34989706446869</v>
       </c>
     </row>
     <row r="9">
@@ -3358,13 +3358,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>86.97499261463339</v>
+        <v>90.63592980376974</v>
       </c>
     </row>
     <row r="10">
@@ -3372,13 +3372,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>99.36268514681969</v>
+        <v>99.0779783125881</v>
       </c>
     </row>
     <row r="11">
@@ -3386,13 +3386,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.285549713215578</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>9.773298395776996</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>110.5271200395144</v>
+        <v>109.8163347016397</v>
       </c>
     </row>
     <row r="12">
@@ -3400,13 +3400,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.810784734987623</v>
+        <v>8.027750977626168</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>115.8599735689831</v>
+        <v>114.5581761131518</v>
       </c>
     </row>
     <row r="13">
@@ -3417,10 +3417,10 @@
         <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>120.9758608558132</v>
+        <v>120.7156977141878</v>
       </c>
     </row>
     <row r="14">
@@ -3428,13 +3428,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8.296749848589794</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="D14" t="n">
-        <v>120.4565163202666</v>
+        <v>121.9929514774129</v>
       </c>
     </row>
     <row r="15">
@@ -3442,13 +3442,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.883434065101886</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="C15" t="n">
         <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>122.1932280090792</v>
+        <v>118.9681868006285</v>
       </c>
     </row>
     <row r="16">
@@ -3456,13 +3456,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.439684102782329</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
         <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>120.6882087784689</v>
+        <v>117.3816825105656</v>
       </c>
     </row>
     <row r="17">
@@ -3476,7 +3476,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>105.3052040006256</v>
+        <v>103.8885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -3490,7 +3490,7 @@
         <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>91.49397729728149</v>
+        <v>93.63418729253954</v>
       </c>
     </row>
     <row r="19">
@@ -3498,13 +3498,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>75.22641783791184</v>
+        <v>71.61554978169207</v>
       </c>
     </row>
     <row r="20">
@@ -3512,13 +3512,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
         <v>20.84741249968101</v>
       </c>
       <c r="D20" t="n">
-        <v>53.12727701531613</v>
+        <v>48.41979677345267</v>
       </c>
     </row>
     <row r="21">
@@ -3526,13 +3526,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>41.00928429022514</v>
+        <v>21.8084676342223</v>
       </c>
       <c r="C21" t="n">
-        <v>61.9907785782473</v>
+        <v>40.26178640164116</v>
       </c>
       <c r="D21" t="n">
-        <v>13.35186000146865</v>
+        <v>5.032723300205145</v>
       </c>
     </row>
   </sheetData>
@@ -3571,13 +3571,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.72255061479242</v>
+        <v>22.54976301884499</v>
       </c>
       <c r="C2" t="n">
-        <v>3.98000519301657</v>
+        <v>4.742823159216341</v>
       </c>
       <c r="D2" t="n">
-        <v>163.5797842293078</v>
+        <v>157.498838949203</v>
       </c>
     </row>
     <row r="3">
@@ -3585,13 +3585,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>58.84104865403258</v>
+        <v>58.33544858634547</v>
       </c>
       <c r="C3" t="n">
-        <v>14.82439033412684</v>
+        <v>17.93653055658923</v>
       </c>
       <c r="D3" t="n">
-        <v>108.3898552873691</v>
+        <v>105.179540294482</v>
       </c>
     </row>
     <row r="4">
@@ -3599,13 +3599,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>97.71138550827655</v>
+        <v>100.6340484238193</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2844701545201</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D4" t="n">
-        <v>73.43669177306991</v>
+        <v>73.16867464981053</v>
       </c>
     </row>
     <row r="5">
@@ -3613,13 +3613,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104.6052178874977</v>
+        <v>108.973995171396</v>
       </c>
       <c r="C5" t="n">
-        <v>13.15541923690726</v>
+        <v>15.75705065316131</v>
       </c>
       <c r="D5" t="n">
-        <v>50.19185137961819</v>
+        <v>50.020045531375</v>
       </c>
     </row>
     <row r="6">
@@ -3627,13 +3627,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>96.56372244201204</v>
+        <v>100.3071264383051</v>
       </c>
       <c r="C6" t="n">
-        <v>7.446556336712058</v>
+        <v>8.211337798320324</v>
       </c>
       <c r="D6" t="n">
-        <v>47.01393406097126</v>
+        <v>46.00764266411829</v>
       </c>
     </row>
     <row r="7">
@@ -3641,13 +3641,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>71.44472568115313</v>
+        <v>69.34869433258619</v>
       </c>
       <c r="C7" t="n">
-        <v>5.928774385946488</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="D7" t="n">
-        <v>56.89227946110266</v>
+        <v>57.01205268102077</v>
       </c>
     </row>
     <row r="8">
@@ -3655,13 +3655,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.95250056176443</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="C8" t="n">
-        <v>6.508987279156353</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="D8" t="n">
-        <v>70.68092596724911</v>
+        <v>71.18161729641498</v>
       </c>
     </row>
     <row r="9">
@@ -3669,13 +3669,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.993749660876023</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
         <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>85.64374272767472</v>
+        <v>88.97186744507141</v>
       </c>
     </row>
     <row r="10">
@@ -3683,13 +3683,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>97.9391509756618</v>
+        <v>97.65444414143025</v>
       </c>
     </row>
     <row r="11">
@@ -3697,13 +3697,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.285549713215578</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>9.773298395776996</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>109.9940310361084</v>
+        <v>108.039371356953</v>
       </c>
     </row>
     <row r="12">
@@ -3711,10 +3711,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.810784734987623</v>
+        <v>8.027750977626168</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
         <v>114.1242436278747</v>
@@ -3728,10 +3728,10 @@
         <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6666888066416</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>119.1547188644354</v>
+        <v>118.6343925811846</v>
       </c>
     </row>
     <row r="14">
@@ -3739,13 +3739,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8.296749848589794</v>
+        <v>7.989462817160544</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="D14" t="n">
-        <v>118.9200811631204</v>
+        <v>120.1492292888374</v>
       </c>
     </row>
     <row r="15">
@@ -3753,13 +3753,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="C15" t="n">
         <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>120.4015384488288</v>
+        <v>117.1764972403781</v>
       </c>
     </row>
     <row r="16">
@@ -3767,13 +3767,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>119.0349456445173</v>
+        <v>115.3151035931261</v>
       </c>
     </row>
     <row r="17">
@@ -3781,13 +3781,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
         <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>104.3607627091402</v>
+        <v>103.4163214176548</v>
       </c>
     </row>
     <row r="18">
@@ -3801,7 +3801,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>90.42387229965247</v>
+        <v>92.029029796096</v>
       </c>
     </row>
     <row r="19">
@@ -3809,13 +3809,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>74.62460649520854</v>
+        <v>70.41192709628548</v>
       </c>
     </row>
     <row r="20">
@@ -3823,13 +3823,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.724971774090649</v>
+        <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
         <v>20.17491532227195</v>
       </c>
       <c r="D20" t="n">
-        <v>53.12727701531613</v>
+        <v>47.74729959604362</v>
       </c>
     </row>
     <row r="21">
@@ -3837,13 +3837,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>44.50791736072754</v>
+        <v>22.19441437572225</v>
       </c>
       <c r="C21" t="n">
-        <v>67.25640845621051</v>
+        <v>41.82793478501501</v>
       </c>
       <c r="D21" t="n">
-        <v>15.82503728381424</v>
+        <v>5.975419255002144</v>
       </c>
     </row>
   </sheetData>
@@ -3882,13 +3882,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.93901813581223</v>
+        <v>34.57813589127691</v>
       </c>
       <c r="C2" t="n">
-        <v>3.145519644406781</v>
+        <v>3.735550014659113</v>
       </c>
       <c r="D2" t="n">
-        <v>172.9780550020625</v>
+        <v>166.4700494706104</v>
       </c>
     </row>
     <row r="3">
@@ -3896,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>77.84768420825083</v>
+        <v>77.641517190359</v>
       </c>
       <c r="C3" t="n">
-        <v>14.72621556370216</v>
+        <v>17.58310138306037</v>
       </c>
       <c r="D3" t="n">
-        <v>131.5640098461151</v>
+        <v>127.4210345341935</v>
       </c>
     </row>
     <row r="4">
@@ -3910,13 +3910,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>116.102465251932</v>
+        <v>118.3104158387831</v>
       </c>
       <c r="C4" t="n">
-        <v>22.20713307006285</v>
+        <v>27.72062817711294</v>
       </c>
       <c r="D4" t="n">
-        <v>80.49447601890023</v>
+        <v>79.8435772909846</v>
       </c>
     </row>
     <row r="5">
@@ -3924,13 +3924,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>140.119941088626</v>
+        <v>145.0532233024663</v>
       </c>
       <c r="C5" t="n">
-        <v>17.20512851692536</v>
+        <v>21.05848825609409</v>
       </c>
       <c r="D5" t="n">
-        <v>52.54804586981054</v>
+        <v>52.35169632896118</v>
       </c>
     </row>
     <row r="6">
@@ -3938,13 +3938,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>135.8090869192783</v>
+        <v>140.8807955594173</v>
       </c>
       <c r="C6" t="n">
-        <v>9.94215900090745</v>
+        <v>11.23021198887927</v>
       </c>
       <c r="D6" t="n">
-        <v>47.69821221083129</v>
+        <v>47.21519234034186</v>
       </c>
     </row>
     <row r="7">
@@ -3952,13 +3952,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>110.0117024947848</v>
+        <v>111.7484141835974</v>
       </c>
       <c r="C7" t="n">
-        <v>6.827073535332318</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="D7" t="n">
-        <v>56.35329997147116</v>
+        <v>56.2934133615121</v>
       </c>
     </row>
     <row r="8">
@@ -3966,13 +3966,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67.67677799225388</v>
+        <v>61.66848204226339</v>
       </c>
       <c r="C8" t="n">
-        <v>6.67588438887831</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="D8" t="n">
-        <v>69.67954330891736</v>
+        <v>70.01333752836128</v>
       </c>
     </row>
     <row r="9">
@@ -3980,13 +3980,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.41093568191868</v>
+        <v>17.9718734739421</v>
       </c>
       <c r="C9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="D9" t="n">
-        <v>85.08905527477528</v>
+        <v>87.30780508637307</v>
       </c>
     </row>
     <row r="10">
@@ -3994,13 +3994,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>96.37326338738815</v>
+        <v>96.23090997027236</v>
       </c>
     </row>
     <row r="11">
@@ -4008,13 +4008,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>9.773298395776996</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>108.2170676914216</v>
+        <v>106.2624080122662</v>
       </c>
     </row>
     <row r="12">
@@ -4022,13 +4022,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.810784734987623</v>
+        <v>8.027750977626168</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>112.6054799294049</v>
+        <v>113.4733448999591</v>
       </c>
     </row>
     <row r="13">
@@ -4039,10 +4039,10 @@
         <v>8.065057390387548</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6666888066416</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>117.3335768730576</v>
+        <v>116.5530874481813</v>
       </c>
     </row>
     <row r="14">
@@ -4050,13 +4050,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8.296749848589794</v>
+        <v>7.989462817160544</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="D14" t="n">
-        <v>117.3836460059741</v>
+        <v>118.3055071002619</v>
       </c>
     </row>
     <row r="15">
@@ -4064,13 +4064,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
         <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>118.6098488885784</v>
+        <v>115.3848076801276</v>
       </c>
     </row>
     <row r="16">
@@ -4078,13 +4078,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
         <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>117.3816825105656</v>
+        <v>114.4884720261503</v>
       </c>
     </row>
     <row r="17">
@@ -4092,13 +4092,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>103.4163214176548</v>
+        <v>101.5274388346839</v>
       </c>
     </row>
     <row r="18">
@@ -4106,13 +4106,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
         <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>89.35376730202346</v>
+        <v>90.42387229965247</v>
       </c>
     </row>
     <row r="19">
@@ -4126,7 +4126,7 @@
         <v>17.45252893839555</v>
       </c>
       <c r="D19" t="n">
-        <v>74.62460649520854</v>
+        <v>69.2083044108789</v>
       </c>
     </row>
     <row r="20">
@@ -4134,13 +4134,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.052474596681584</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>52.45477983790707</v>
+        <v>47.07480241863455</v>
       </c>
     </row>
     <row r="21">
@@ -4148,13 +4148,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>47.07717691904259</v>
+        <v>22.56416150660399</v>
       </c>
       <c r="C21" t="n">
-        <v>72.66259915765269</v>
+        <v>43.39261828193074</v>
       </c>
       <c r="D21" t="n">
-        <v>18.42150401179927</v>
+        <v>6.942818925108918</v>
       </c>
     </row>
   </sheetData>
